--- a/oi_pcr_dashboard.xlsx
+++ b/oi_pcr_dashboard.xlsx
@@ -535,7 +535,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM582"/>
+  <dimension ref="A1:AM584"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4" outlineLevelCol="0"/>
   <cols>
     <col width="8.88671875" customWidth="1" style="1" min="1" max="3"/>
@@ -48064,18 +48064,6 @@
           <t>[(24000, 10724400, 14581200), (23000, 9491325, 11745075), (24400, 8574825, 18093150)]</t>
         </is>
       </c>
-      <c r="AB462" t="inlineStr"/>
-      <c r="AC462" t="inlineStr"/>
-      <c r="AD462" t="inlineStr"/>
-      <c r="AE462" t="inlineStr"/>
-      <c r="AF462" t="inlineStr"/>
-      <c r="AG462" t="inlineStr"/>
-      <c r="AH462" t="inlineStr"/>
-      <c r="AI462" t="inlineStr"/>
-      <c r="AJ462" t="inlineStr"/>
-      <c r="AK462" t="inlineStr"/>
-      <c r="AL462" t="inlineStr"/>
-      <c r="AM462" t="inlineStr"/>
     </row>
     <row r="463">
       <c r="A463" t="inlineStr">
@@ -48179,18 +48167,6 @@
           <t>[(24000, 10703775, 14555400), (23000, 9491625, 11745375), (24400, 8498475, 18069450)]</t>
         </is>
       </c>
-      <c r="AB463" t="inlineStr"/>
-      <c r="AC463" t="inlineStr"/>
-      <c r="AD463" t="inlineStr"/>
-      <c r="AE463" t="inlineStr"/>
-      <c r="AF463" t="inlineStr"/>
-      <c r="AG463" t="inlineStr"/>
-      <c r="AH463" t="inlineStr"/>
-      <c r="AI463" t="inlineStr"/>
-      <c r="AJ463" t="inlineStr"/>
-      <c r="AK463" t="inlineStr"/>
-      <c r="AL463" t="inlineStr"/>
-      <c r="AM463" t="inlineStr"/>
     </row>
     <row r="464">
       <c r="A464" t="inlineStr">
@@ -48294,18 +48270,6 @@
           <t>[(24000, 10703775, 14555400), (23000, 9491625, 11745375), (24400, 8498475, 18069450)]</t>
         </is>
       </c>
-      <c r="AB464" t="inlineStr"/>
-      <c r="AC464" t="inlineStr"/>
-      <c r="AD464" t="inlineStr"/>
-      <c r="AE464" t="inlineStr"/>
-      <c r="AF464" t="inlineStr"/>
-      <c r="AG464" t="inlineStr"/>
-      <c r="AH464" t="inlineStr"/>
-      <c r="AI464" t="inlineStr"/>
-      <c r="AJ464" t="inlineStr"/>
-      <c r="AK464" t="inlineStr"/>
-      <c r="AL464" t="inlineStr"/>
-      <c r="AM464" t="inlineStr"/>
     </row>
     <row r="465">
       <c r="A465" t="inlineStr">
@@ -48409,18 +48373,6 @@
           <t>[(24000, 10689150, 14540100), (23000, 9413550, 11667300), (24400, 8556525, 18078225)]</t>
         </is>
       </c>
-      <c r="AB465" t="inlineStr"/>
-      <c r="AC465" t="inlineStr"/>
-      <c r="AD465" t="inlineStr"/>
-      <c r="AE465" t="inlineStr"/>
-      <c r="AF465" t="inlineStr"/>
-      <c r="AG465" t="inlineStr"/>
-      <c r="AH465" t="inlineStr"/>
-      <c r="AI465" t="inlineStr"/>
-      <c r="AJ465" t="inlineStr"/>
-      <c r="AK465" t="inlineStr"/>
-      <c r="AL465" t="inlineStr"/>
-      <c r="AM465" t="inlineStr"/>
     </row>
     <row r="466">
       <c r="A466" t="inlineStr">
@@ -48524,18 +48476,6 @@
           <t>[(24000, 10689150, 14540100), (23000, 9413550, 11665875), (24400, 8556525, 18078225)]</t>
         </is>
       </c>
-      <c r="AB466" t="inlineStr"/>
-      <c r="AC466" t="inlineStr"/>
-      <c r="AD466" t="inlineStr"/>
-      <c r="AE466" t="inlineStr"/>
-      <c r="AF466" t="inlineStr"/>
-      <c r="AG466" t="inlineStr"/>
-      <c r="AH466" t="inlineStr"/>
-      <c r="AI466" t="inlineStr"/>
-      <c r="AJ466" t="inlineStr"/>
-      <c r="AK466" t="inlineStr"/>
-      <c r="AL466" t="inlineStr"/>
-      <c r="AM466" t="inlineStr"/>
     </row>
     <row r="467">
       <c r="A467" t="inlineStr">
@@ -48639,18 +48579,6 @@
           <t>[(24000, 10689150, 14540100), (23000, 9413550, 11665875), (24400, 8556525, 18078225)]</t>
         </is>
       </c>
-      <c r="AB467" t="inlineStr"/>
-      <c r="AC467" t="inlineStr"/>
-      <c r="AD467" t="inlineStr"/>
-      <c r="AE467" t="inlineStr"/>
-      <c r="AF467" t="inlineStr"/>
-      <c r="AG467" t="inlineStr"/>
-      <c r="AH467" t="inlineStr"/>
-      <c r="AI467" t="inlineStr"/>
-      <c r="AJ467" t="inlineStr"/>
-      <c r="AK467" t="inlineStr"/>
-      <c r="AL467" t="inlineStr"/>
-      <c r="AM467" t="inlineStr"/>
     </row>
     <row r="468">
       <c r="A468" t="inlineStr">
@@ -48754,18 +48682,6 @@
           <t>[(24000, 10710075, 14559450), (23000, 9410775, 11663025), (24400, 8682750, 18146400)]</t>
         </is>
       </c>
-      <c r="AB468" t="inlineStr"/>
-      <c r="AC468" t="inlineStr"/>
-      <c r="AD468" t="inlineStr"/>
-      <c r="AE468" t="inlineStr"/>
-      <c r="AF468" t="inlineStr"/>
-      <c r="AG468" t="inlineStr"/>
-      <c r="AH468" t="inlineStr"/>
-      <c r="AI468" t="inlineStr"/>
-      <c r="AJ468" t="inlineStr"/>
-      <c r="AK468" t="inlineStr"/>
-      <c r="AL468" t="inlineStr"/>
-      <c r="AM468" t="inlineStr"/>
     </row>
     <row r="469">
       <c r="A469" t="inlineStr">
@@ -48869,18 +48785,6 @@
           <t>[(24000, 10710075, 14559450), (23000, 9410775, 11663025), (24400, 8682750, 18146400)]</t>
         </is>
       </c>
-      <c r="AB469" t="inlineStr"/>
-      <c r="AC469" t="inlineStr"/>
-      <c r="AD469" t="inlineStr"/>
-      <c r="AE469" t="inlineStr"/>
-      <c r="AF469" t="inlineStr"/>
-      <c r="AG469" t="inlineStr"/>
-      <c r="AH469" t="inlineStr"/>
-      <c r="AI469" t="inlineStr"/>
-      <c r="AJ469" t="inlineStr"/>
-      <c r="AK469" t="inlineStr"/>
-      <c r="AL469" t="inlineStr"/>
-      <c r="AM469" t="inlineStr"/>
     </row>
     <row r="470">
       <c r="A470" t="inlineStr">
@@ -48984,18 +48888,6 @@
           <t>[(24000, 10710075, 14559450), (23000, 9410775, 11663025), (24400, 8682750, 18146400)]</t>
         </is>
       </c>
-      <c r="AB470" t="inlineStr"/>
-      <c r="AC470" t="inlineStr"/>
-      <c r="AD470" t="inlineStr"/>
-      <c r="AE470" t="inlineStr"/>
-      <c r="AF470" t="inlineStr"/>
-      <c r="AG470" t="inlineStr"/>
-      <c r="AH470" t="inlineStr"/>
-      <c r="AI470" t="inlineStr"/>
-      <c r="AJ470" t="inlineStr"/>
-      <c r="AK470" t="inlineStr"/>
-      <c r="AL470" t="inlineStr"/>
-      <c r="AM470" t="inlineStr"/>
     </row>
     <row r="471">
       <c r="A471" t="inlineStr">
@@ -49099,18 +48991,6 @@
           <t>[(24000, 10705725, 14553900), (23000, 9444825, 11697075), (24400, 8738325, 18152625)]</t>
         </is>
       </c>
-      <c r="AB471" t="inlineStr"/>
-      <c r="AC471" t="inlineStr"/>
-      <c r="AD471" t="inlineStr"/>
-      <c r="AE471" t="inlineStr"/>
-      <c r="AF471" t="inlineStr"/>
-      <c r="AG471" t="inlineStr"/>
-      <c r="AH471" t="inlineStr"/>
-      <c r="AI471" t="inlineStr"/>
-      <c r="AJ471" t="inlineStr"/>
-      <c r="AK471" t="inlineStr"/>
-      <c r="AL471" t="inlineStr"/>
-      <c r="AM471" t="inlineStr"/>
     </row>
     <row r="472">
       <c r="A472" t="inlineStr">
@@ -49214,18 +49094,6 @@
           <t>[(24000, 10705725, 14553900), (23000, 9444825, 11697450), (24400, 8738325, 18152625)]</t>
         </is>
       </c>
-      <c r="AB472" t="inlineStr"/>
-      <c r="AC472" t="inlineStr"/>
-      <c r="AD472" t="inlineStr"/>
-      <c r="AE472" t="inlineStr"/>
-      <c r="AF472" t="inlineStr"/>
-      <c r="AG472" t="inlineStr"/>
-      <c r="AH472" t="inlineStr"/>
-      <c r="AI472" t="inlineStr"/>
-      <c r="AJ472" t="inlineStr"/>
-      <c r="AK472" t="inlineStr"/>
-      <c r="AL472" t="inlineStr"/>
-      <c r="AM472" t="inlineStr"/>
     </row>
     <row r="473">
       <c r="A473" t="inlineStr">
@@ -49329,18 +49197,6 @@
           <t>[(24000, 10705725, 14553900), (23000, 9444825, 11697450), (24400, 8738325, 18152625)]</t>
         </is>
       </c>
-      <c r="AB473" t="inlineStr"/>
-      <c r="AC473" t="inlineStr"/>
-      <c r="AD473" t="inlineStr"/>
-      <c r="AE473" t="inlineStr"/>
-      <c r="AF473" t="inlineStr"/>
-      <c r="AG473" t="inlineStr"/>
-      <c r="AH473" t="inlineStr"/>
-      <c r="AI473" t="inlineStr"/>
-      <c r="AJ473" t="inlineStr"/>
-      <c r="AK473" t="inlineStr"/>
-      <c r="AL473" t="inlineStr"/>
-      <c r="AM473" t="inlineStr"/>
     </row>
     <row r="474">
       <c r="A474" t="inlineStr">
@@ -49444,18 +49300,6 @@
           <t>[(24000, 10719750, 14568225), (23000, 9435675, 11688300), (24400, 8820750, 18171675)]</t>
         </is>
       </c>
-      <c r="AB474" t="inlineStr"/>
-      <c r="AC474" t="inlineStr"/>
-      <c r="AD474" t="inlineStr"/>
-      <c r="AE474" t="inlineStr"/>
-      <c r="AF474" t="inlineStr"/>
-      <c r="AG474" t="inlineStr"/>
-      <c r="AH474" t="inlineStr"/>
-      <c r="AI474" t="inlineStr"/>
-      <c r="AJ474" t="inlineStr"/>
-      <c r="AK474" t="inlineStr"/>
-      <c r="AL474" t="inlineStr"/>
-      <c r="AM474" t="inlineStr"/>
     </row>
     <row r="475">
       <c r="A475" t="inlineStr">
@@ -49559,18 +49403,6 @@
           <t>[(24000, 10719750, 14568225), (23000, 9435675, 11688300), (24400, 8820750, 18171675)]</t>
         </is>
       </c>
-      <c r="AB475" t="inlineStr"/>
-      <c r="AC475" t="inlineStr"/>
-      <c r="AD475" t="inlineStr"/>
-      <c r="AE475" t="inlineStr"/>
-      <c r="AF475" t="inlineStr"/>
-      <c r="AG475" t="inlineStr"/>
-      <c r="AH475" t="inlineStr"/>
-      <c r="AI475" t="inlineStr"/>
-      <c r="AJ475" t="inlineStr"/>
-      <c r="AK475" t="inlineStr"/>
-      <c r="AL475" t="inlineStr"/>
-      <c r="AM475" t="inlineStr"/>
     </row>
     <row r="476">
       <c r="A476" t="inlineStr">
@@ -49674,18 +49506,6 @@
           <t>[(24000, 10719750, 14568225), (23000, 9435675, 11688300), (24400, 8820750, 18171675)]</t>
         </is>
       </c>
-      <c r="AB476" t="inlineStr"/>
-      <c r="AC476" t="inlineStr"/>
-      <c r="AD476" t="inlineStr"/>
-      <c r="AE476" t="inlineStr"/>
-      <c r="AF476" t="inlineStr"/>
-      <c r="AG476" t="inlineStr"/>
-      <c r="AH476" t="inlineStr"/>
-      <c r="AI476" t="inlineStr"/>
-      <c r="AJ476" t="inlineStr"/>
-      <c r="AK476" t="inlineStr"/>
-      <c r="AL476" t="inlineStr"/>
-      <c r="AM476" t="inlineStr"/>
     </row>
     <row r="477">
       <c r="A477" t="inlineStr">
@@ -49789,18 +49609,6 @@
           <t>[(24000, 10736625, 14581650), (23000, 9478500, 11731125), (24400, 8924925, 18224550)]</t>
         </is>
       </c>
-      <c r="AB477" t="inlineStr"/>
-      <c r="AC477" t="inlineStr"/>
-      <c r="AD477" t="inlineStr"/>
-      <c r="AE477" t="inlineStr"/>
-      <c r="AF477" t="inlineStr"/>
-      <c r="AG477" t="inlineStr"/>
-      <c r="AH477" t="inlineStr"/>
-      <c r="AI477" t="inlineStr"/>
-      <c r="AJ477" t="inlineStr"/>
-      <c r="AK477" t="inlineStr"/>
-      <c r="AL477" t="inlineStr"/>
-      <c r="AM477" t="inlineStr"/>
     </row>
     <row r="478">
       <c r="A478" t="inlineStr">
@@ -49904,18 +49712,6 @@
           <t>[(24000, 10736625, 14581650), (23000, 9478500, 11731125), (24400, 8924925, 18224550)]</t>
         </is>
       </c>
-      <c r="AB478" t="inlineStr"/>
-      <c r="AC478" t="inlineStr"/>
-      <c r="AD478" t="inlineStr"/>
-      <c r="AE478" t="inlineStr"/>
-      <c r="AF478" t="inlineStr"/>
-      <c r="AG478" t="inlineStr"/>
-      <c r="AH478" t="inlineStr"/>
-      <c r="AI478" t="inlineStr"/>
-      <c r="AJ478" t="inlineStr"/>
-      <c r="AK478" t="inlineStr"/>
-      <c r="AL478" t="inlineStr"/>
-      <c r="AM478" t="inlineStr"/>
     </row>
     <row r="479">
       <c r="A479" t="inlineStr">
@@ -50019,18 +49815,6 @@
           <t>[(24000, 10736625, 14581650), (23000, 9478500, 11730750), (24400, 8924925, 18224550)]</t>
         </is>
       </c>
-      <c r="AB479" t="inlineStr"/>
-      <c r="AC479" t="inlineStr"/>
-      <c r="AD479" t="inlineStr"/>
-      <c r="AE479" t="inlineStr"/>
-      <c r="AF479" t="inlineStr"/>
-      <c r="AG479" t="inlineStr"/>
-      <c r="AH479" t="inlineStr"/>
-      <c r="AI479" t="inlineStr"/>
-      <c r="AJ479" t="inlineStr"/>
-      <c r="AK479" t="inlineStr"/>
-      <c r="AL479" t="inlineStr"/>
-      <c r="AM479" t="inlineStr"/>
     </row>
     <row r="480">
       <c r="A480" t="inlineStr">
@@ -50134,18 +49918,6 @@
           <t>[(24000, 10785450, 14627625), (23000, 9508200, 11760450), (24400, 8929575, 18067875)]</t>
         </is>
       </c>
-      <c r="AB480" t="inlineStr"/>
-      <c r="AC480" t="inlineStr"/>
-      <c r="AD480" t="inlineStr"/>
-      <c r="AE480" t="inlineStr"/>
-      <c r="AF480" t="inlineStr"/>
-      <c r="AG480" t="inlineStr"/>
-      <c r="AH480" t="inlineStr"/>
-      <c r="AI480" t="inlineStr"/>
-      <c r="AJ480" t="inlineStr"/>
-      <c r="AK480" t="inlineStr"/>
-      <c r="AL480" t="inlineStr"/>
-      <c r="AM480" t="inlineStr"/>
     </row>
     <row r="481">
       <c r="A481" t="inlineStr">
@@ -50249,18 +50021,6 @@
           <t>[(24000, 10785450, 14627625), (23000, 9508200, 11760225), (24400, 8929575, 18067875)]</t>
         </is>
       </c>
-      <c r="AB481" t="inlineStr"/>
-      <c r="AC481" t="inlineStr"/>
-      <c r="AD481" t="inlineStr"/>
-      <c r="AE481" t="inlineStr"/>
-      <c r="AF481" t="inlineStr"/>
-      <c r="AG481" t="inlineStr"/>
-      <c r="AH481" t="inlineStr"/>
-      <c r="AI481" t="inlineStr"/>
-      <c r="AJ481" t="inlineStr"/>
-      <c r="AK481" t="inlineStr"/>
-      <c r="AL481" t="inlineStr"/>
-      <c r="AM481" t="inlineStr"/>
     </row>
     <row r="482">
       <c r="A482" t="inlineStr">
@@ -50364,18 +50124,6 @@
           <t>[(24000, 10785450, 14627625), (23000, 9508200, 11760225), (24400, 8929575, 18067875)]</t>
         </is>
       </c>
-      <c r="AB482" t="inlineStr"/>
-      <c r="AC482" t="inlineStr"/>
-      <c r="AD482" t="inlineStr"/>
-      <c r="AE482" t="inlineStr"/>
-      <c r="AF482" t="inlineStr"/>
-      <c r="AG482" t="inlineStr"/>
-      <c r="AH482" t="inlineStr"/>
-      <c r="AI482" t="inlineStr"/>
-      <c r="AJ482" t="inlineStr"/>
-      <c r="AK482" t="inlineStr"/>
-      <c r="AL482" t="inlineStr"/>
-      <c r="AM482" t="inlineStr"/>
     </row>
     <row r="483">
       <c r="A483" t="inlineStr">
@@ -50479,18 +50227,6 @@
           <t>[(24000, 10759050, 14598075), (23000, 9598050, 11850075), (24400, 8799675, 17898525)]</t>
         </is>
       </c>
-      <c r="AB483" t="inlineStr"/>
-      <c r="AC483" t="inlineStr"/>
-      <c r="AD483" t="inlineStr"/>
-      <c r="AE483" t="inlineStr"/>
-      <c r="AF483" t="inlineStr"/>
-      <c r="AG483" t="inlineStr"/>
-      <c r="AH483" t="inlineStr"/>
-      <c r="AI483" t="inlineStr"/>
-      <c r="AJ483" t="inlineStr"/>
-      <c r="AK483" t="inlineStr"/>
-      <c r="AL483" t="inlineStr"/>
-      <c r="AM483" t="inlineStr"/>
     </row>
     <row r="484">
       <c r="A484" t="inlineStr">
@@ -50594,18 +50330,6 @@
           <t>[(24000, 10759050, 14598075), (23000, 9598050, 11849550), (24400, 8799675, 17898525)]</t>
         </is>
       </c>
-      <c r="AB484" t="inlineStr"/>
-      <c r="AC484" t="inlineStr"/>
-      <c r="AD484" t="inlineStr"/>
-      <c r="AE484" t="inlineStr"/>
-      <c r="AF484" t="inlineStr"/>
-      <c r="AG484" t="inlineStr"/>
-      <c r="AH484" t="inlineStr"/>
-      <c r="AI484" t="inlineStr"/>
-      <c r="AJ484" t="inlineStr"/>
-      <c r="AK484" t="inlineStr"/>
-      <c r="AL484" t="inlineStr"/>
-      <c r="AM484" t="inlineStr"/>
     </row>
     <row r="485">
       <c r="A485" t="inlineStr">
@@ -50709,18 +50433,6 @@
           <t>[(24000, 10759050, 14598075), (23000, 9598050, 11849550), (24400, 8799675, 17898525)]</t>
         </is>
       </c>
-      <c r="AB485" t="inlineStr"/>
-      <c r="AC485" t="inlineStr"/>
-      <c r="AD485" t="inlineStr"/>
-      <c r="AE485" t="inlineStr"/>
-      <c r="AF485" t="inlineStr"/>
-      <c r="AG485" t="inlineStr"/>
-      <c r="AH485" t="inlineStr"/>
-      <c r="AI485" t="inlineStr"/>
-      <c r="AJ485" t="inlineStr"/>
-      <c r="AK485" t="inlineStr"/>
-      <c r="AL485" t="inlineStr"/>
-      <c r="AM485" t="inlineStr"/>
     </row>
     <row r="486">
       <c r="A486" t="inlineStr">
@@ -50824,18 +50536,6 @@
           <t>[(24000, 10703925, 14539050), (23000, 9601950, 11853750), (24400, 8637525, 17598825)]</t>
         </is>
       </c>
-      <c r="AB486" t="inlineStr"/>
-      <c r="AC486" t="inlineStr"/>
-      <c r="AD486" t="inlineStr"/>
-      <c r="AE486" t="inlineStr"/>
-      <c r="AF486" t="inlineStr"/>
-      <c r="AG486" t="inlineStr"/>
-      <c r="AH486" t="inlineStr"/>
-      <c r="AI486" t="inlineStr"/>
-      <c r="AJ486" t="inlineStr"/>
-      <c r="AK486" t="inlineStr"/>
-      <c r="AL486" t="inlineStr"/>
-      <c r="AM486" t="inlineStr"/>
     </row>
     <row r="487">
       <c r="A487" t="inlineStr">
@@ -50939,18 +50639,6 @@
           <t>[(24000, 10703925, 14539050), (23000, 9601950, 11853750), (24400, 8637525, 17598825)]</t>
         </is>
       </c>
-      <c r="AB487" t="inlineStr"/>
-      <c r="AC487" t="inlineStr"/>
-      <c r="AD487" t="inlineStr"/>
-      <c r="AE487" t="inlineStr"/>
-      <c r="AF487" t="inlineStr"/>
-      <c r="AG487" t="inlineStr"/>
-      <c r="AH487" t="inlineStr"/>
-      <c r="AI487" t="inlineStr"/>
-      <c r="AJ487" t="inlineStr"/>
-      <c r="AK487" t="inlineStr"/>
-      <c r="AL487" t="inlineStr"/>
-      <c r="AM487" t="inlineStr"/>
     </row>
     <row r="488">
       <c r="A488" t="inlineStr">
@@ -51054,18 +50742,6 @@
           <t>[(24000, 10703925, 14539050), (23000, 9601950, 11853750), (24400, 8637525, 17598825)]</t>
         </is>
       </c>
-      <c r="AB488" t="inlineStr"/>
-      <c r="AC488" t="inlineStr"/>
-      <c r="AD488" t="inlineStr"/>
-      <c r="AE488" t="inlineStr"/>
-      <c r="AF488" t="inlineStr"/>
-      <c r="AG488" t="inlineStr"/>
-      <c r="AH488" t="inlineStr"/>
-      <c r="AI488" t="inlineStr"/>
-      <c r="AJ488" t="inlineStr"/>
-      <c r="AK488" t="inlineStr"/>
-      <c r="AL488" t="inlineStr"/>
-      <c r="AM488" t="inlineStr"/>
     </row>
     <row r="489">
       <c r="A489" t="inlineStr">
@@ -51169,18 +50845,6 @@
           <t>[(24000, 10739925, 14570400), (23000, 9576975, 11828100), (24400, 8707050, 17513025)]</t>
         </is>
       </c>
-      <c r="AB489" t="inlineStr"/>
-      <c r="AC489" t="inlineStr"/>
-      <c r="AD489" t="inlineStr"/>
-      <c r="AE489" t="inlineStr"/>
-      <c r="AF489" t="inlineStr"/>
-      <c r="AG489" t="inlineStr"/>
-      <c r="AH489" t="inlineStr"/>
-      <c r="AI489" t="inlineStr"/>
-      <c r="AJ489" t="inlineStr"/>
-      <c r="AK489" t="inlineStr"/>
-      <c r="AL489" t="inlineStr"/>
-      <c r="AM489" t="inlineStr"/>
     </row>
     <row r="490">
       <c r="A490" t="inlineStr">
@@ -51284,18 +50948,6 @@
           <t>[(24000, 10739925, 14570400), (23000, 9576975, 11828100), (24400, 8707050, 17513025)]</t>
         </is>
       </c>
-      <c r="AB490" t="inlineStr"/>
-      <c r="AC490" t="inlineStr"/>
-      <c r="AD490" t="inlineStr"/>
-      <c r="AE490" t="inlineStr"/>
-      <c r="AF490" t="inlineStr"/>
-      <c r="AG490" t="inlineStr"/>
-      <c r="AH490" t="inlineStr"/>
-      <c r="AI490" t="inlineStr"/>
-      <c r="AJ490" t="inlineStr"/>
-      <c r="AK490" t="inlineStr"/>
-      <c r="AL490" t="inlineStr"/>
-      <c r="AM490" t="inlineStr"/>
     </row>
     <row r="491">
       <c r="A491" t="inlineStr">
@@ -51399,18 +51051,6 @@
           <t>[(24000, 10739925, 14570400), (23000, 9576975, 11828100), (24400, 8707050, 17513025)]</t>
         </is>
       </c>
-      <c r="AB491" t="inlineStr"/>
-      <c r="AC491" t="inlineStr"/>
-      <c r="AD491" t="inlineStr"/>
-      <c r="AE491" t="inlineStr"/>
-      <c r="AF491" t="inlineStr"/>
-      <c r="AG491" t="inlineStr"/>
-      <c r="AH491" t="inlineStr"/>
-      <c r="AI491" t="inlineStr"/>
-      <c r="AJ491" t="inlineStr"/>
-      <c r="AK491" t="inlineStr"/>
-      <c r="AL491" t="inlineStr"/>
-      <c r="AM491" t="inlineStr"/>
     </row>
     <row r="492">
       <c r="A492" t="inlineStr">
@@ -51514,18 +51154,6 @@
           <t>[(24000, 10745700, 14575875), (23000, 9648075, 11898300), (24400, 8696475, 17388825)]</t>
         </is>
       </c>
-      <c r="AB492" t="inlineStr"/>
-      <c r="AC492" t="inlineStr"/>
-      <c r="AD492" t="inlineStr"/>
-      <c r="AE492" t="inlineStr"/>
-      <c r="AF492" t="inlineStr"/>
-      <c r="AG492" t="inlineStr"/>
-      <c r="AH492" t="inlineStr"/>
-      <c r="AI492" t="inlineStr"/>
-      <c r="AJ492" t="inlineStr"/>
-      <c r="AK492" t="inlineStr"/>
-      <c r="AL492" t="inlineStr"/>
-      <c r="AM492" t="inlineStr"/>
     </row>
     <row r="493">
       <c r="A493" t="inlineStr">
@@ -51629,18 +51257,6 @@
           <t>[(24000, 10745700, 14575875), (23000, 9648075, 11898300), (24400, 8696475, 17388825)]</t>
         </is>
       </c>
-      <c r="AB493" t="inlineStr"/>
-      <c r="AC493" t="inlineStr"/>
-      <c r="AD493" t="inlineStr"/>
-      <c r="AE493" t="inlineStr"/>
-      <c r="AF493" t="inlineStr"/>
-      <c r="AG493" t="inlineStr"/>
-      <c r="AH493" t="inlineStr"/>
-      <c r="AI493" t="inlineStr"/>
-      <c r="AJ493" t="inlineStr"/>
-      <c r="AK493" t="inlineStr"/>
-      <c r="AL493" t="inlineStr"/>
-      <c r="AM493" t="inlineStr"/>
     </row>
     <row r="494">
       <c r="A494" t="inlineStr">
@@ -51744,18 +51360,6 @@
           <t>[(24000, 10745700, 14575875), (23000, 9648075, 11898300), (24400, 8696475, 17388825)]</t>
         </is>
       </c>
-      <c r="AB494" t="inlineStr"/>
-      <c r="AC494" t="inlineStr"/>
-      <c r="AD494" t="inlineStr"/>
-      <c r="AE494" t="inlineStr"/>
-      <c r="AF494" t="inlineStr"/>
-      <c r="AG494" t="inlineStr"/>
-      <c r="AH494" t="inlineStr"/>
-      <c r="AI494" t="inlineStr"/>
-      <c r="AJ494" t="inlineStr"/>
-      <c r="AK494" t="inlineStr"/>
-      <c r="AL494" t="inlineStr"/>
-      <c r="AM494" t="inlineStr"/>
     </row>
     <row r="495">
       <c r="A495" t="inlineStr">
@@ -51859,18 +51463,6 @@
           <t>[(24000, 10723350, 14551650), (23000, 9648975, 11899200), (24400, 8736000, 17557800)]</t>
         </is>
       </c>
-      <c r="AB495" t="inlineStr"/>
-      <c r="AC495" t="inlineStr"/>
-      <c r="AD495" t="inlineStr"/>
-      <c r="AE495" t="inlineStr"/>
-      <c r="AF495" t="inlineStr"/>
-      <c r="AG495" t="inlineStr"/>
-      <c r="AH495" t="inlineStr"/>
-      <c r="AI495" t="inlineStr"/>
-      <c r="AJ495" t="inlineStr"/>
-      <c r="AK495" t="inlineStr"/>
-      <c r="AL495" t="inlineStr"/>
-      <c r="AM495" t="inlineStr"/>
     </row>
     <row r="496">
       <c r="A496" t="inlineStr">
@@ -51974,18 +51566,6 @@
           <t>[(24000, 10723350, 14551650), (23000, 9648975, 11898750), (24400, 8736000, 17557800)]</t>
         </is>
       </c>
-      <c r="AB496" t="inlineStr"/>
-      <c r="AC496" t="inlineStr"/>
-      <c r="AD496" t="inlineStr"/>
-      <c r="AE496" t="inlineStr"/>
-      <c r="AF496" t="inlineStr"/>
-      <c r="AG496" t="inlineStr"/>
-      <c r="AH496" t="inlineStr"/>
-      <c r="AI496" t="inlineStr"/>
-      <c r="AJ496" t="inlineStr"/>
-      <c r="AK496" t="inlineStr"/>
-      <c r="AL496" t="inlineStr"/>
-      <c r="AM496" t="inlineStr"/>
     </row>
     <row r="497">
       <c r="A497" t="inlineStr">
@@ -52089,18 +51669,6 @@
           <t>[(24000, 10723350, 14551650), (23000, 9648975, 11898750), (24400, 8736000, 17557800)]</t>
         </is>
       </c>
-      <c r="AB497" t="inlineStr"/>
-      <c r="AC497" t="inlineStr"/>
-      <c r="AD497" t="inlineStr"/>
-      <c r="AE497" t="inlineStr"/>
-      <c r="AF497" t="inlineStr"/>
-      <c r="AG497" t="inlineStr"/>
-      <c r="AH497" t="inlineStr"/>
-      <c r="AI497" t="inlineStr"/>
-      <c r="AJ497" t="inlineStr"/>
-      <c r="AK497" t="inlineStr"/>
-      <c r="AL497" t="inlineStr"/>
-      <c r="AM497" t="inlineStr"/>
     </row>
     <row r="498">
       <c r="A498" t="inlineStr">
@@ -52204,18 +51772,6 @@
           <t>[(24000, 10768200, 14593650), (23000, 9662775, 11912025), (24400, 8939700, 17640300)]</t>
         </is>
       </c>
-      <c r="AB498" t="inlineStr"/>
-      <c r="AC498" t="inlineStr"/>
-      <c r="AD498" t="inlineStr"/>
-      <c r="AE498" t="inlineStr"/>
-      <c r="AF498" t="inlineStr"/>
-      <c r="AG498" t="inlineStr"/>
-      <c r="AH498" t="inlineStr"/>
-      <c r="AI498" t="inlineStr"/>
-      <c r="AJ498" t="inlineStr"/>
-      <c r="AK498" t="inlineStr"/>
-      <c r="AL498" t="inlineStr"/>
-      <c r="AM498" t="inlineStr"/>
     </row>
     <row r="499">
       <c r="A499" t="inlineStr">
@@ -52319,18 +51875,6 @@
           <t>[(24000, 10768200, 14593650), (23000, 9662775, 11912025), (24400, 8939700, 17640300)]</t>
         </is>
       </c>
-      <c r="AB499" t="inlineStr"/>
-      <c r="AC499" t="inlineStr"/>
-      <c r="AD499" t="inlineStr"/>
-      <c r="AE499" t="inlineStr"/>
-      <c r="AF499" t="inlineStr"/>
-      <c r="AG499" t="inlineStr"/>
-      <c r="AH499" t="inlineStr"/>
-      <c r="AI499" t="inlineStr"/>
-      <c r="AJ499" t="inlineStr"/>
-      <c r="AK499" t="inlineStr"/>
-      <c r="AL499" t="inlineStr"/>
-      <c r="AM499" t="inlineStr"/>
     </row>
     <row r="500">
       <c r="A500" t="inlineStr">
@@ -52434,18 +51978,6 @@
           <t>[(24000, 10768200, 14593650), (23000, 9662775, 11912025), (24400, 8939700, 17640300)]</t>
         </is>
       </c>
-      <c r="AB500" t="inlineStr"/>
-      <c r="AC500" t="inlineStr"/>
-      <c r="AD500" t="inlineStr"/>
-      <c r="AE500" t="inlineStr"/>
-      <c r="AF500" t="inlineStr"/>
-      <c r="AG500" t="inlineStr"/>
-      <c r="AH500" t="inlineStr"/>
-      <c r="AI500" t="inlineStr"/>
-      <c r="AJ500" t="inlineStr"/>
-      <c r="AK500" t="inlineStr"/>
-      <c r="AL500" t="inlineStr"/>
-      <c r="AM500" t="inlineStr"/>
     </row>
     <row r="501">
       <c r="A501" t="inlineStr">
@@ -52549,18 +52081,6 @@
           <t>[(24000, 10762950, 14588400), (23000, 9652050, 11901300), (24400, 8913975, 17704200)]</t>
         </is>
       </c>
-      <c r="AB501" t="inlineStr"/>
-      <c r="AC501" t="inlineStr"/>
-      <c r="AD501" t="inlineStr"/>
-      <c r="AE501" t="inlineStr"/>
-      <c r="AF501" t="inlineStr"/>
-      <c r="AG501" t="inlineStr"/>
-      <c r="AH501" t="inlineStr"/>
-      <c r="AI501" t="inlineStr"/>
-      <c r="AJ501" t="inlineStr"/>
-      <c r="AK501" t="inlineStr"/>
-      <c r="AL501" t="inlineStr"/>
-      <c r="AM501" t="inlineStr"/>
     </row>
     <row r="502">
       <c r="A502" t="inlineStr">
@@ -52664,18 +52184,6 @@
           <t>[(24000, 10762950, 14588400), (23000, 9652050, 11901225), (24400, 8913975, 17704200)]</t>
         </is>
       </c>
-      <c r="AB502" t="inlineStr"/>
-      <c r="AC502" t="inlineStr"/>
-      <c r="AD502" t="inlineStr"/>
-      <c r="AE502" t="inlineStr"/>
-      <c r="AF502" t="inlineStr"/>
-      <c r="AG502" t="inlineStr"/>
-      <c r="AH502" t="inlineStr"/>
-      <c r="AI502" t="inlineStr"/>
-      <c r="AJ502" t="inlineStr"/>
-      <c r="AK502" t="inlineStr"/>
-      <c r="AL502" t="inlineStr"/>
-      <c r="AM502" t="inlineStr"/>
     </row>
     <row r="503">
       <c r="A503" t="inlineStr">
@@ -52779,18 +52287,6 @@
           <t>[(24000, 10762950, 14588400), (23000, 9652050, 11901225), (24400, 8913975, 17704200)]</t>
         </is>
       </c>
-      <c r="AB503" t="inlineStr"/>
-      <c r="AC503" t="inlineStr"/>
-      <c r="AD503" t="inlineStr"/>
-      <c r="AE503" t="inlineStr"/>
-      <c r="AF503" t="inlineStr"/>
-      <c r="AG503" t="inlineStr"/>
-      <c r="AH503" t="inlineStr"/>
-      <c r="AI503" t="inlineStr"/>
-      <c r="AJ503" t="inlineStr"/>
-      <c r="AK503" t="inlineStr"/>
-      <c r="AL503" t="inlineStr"/>
-      <c r="AM503" t="inlineStr"/>
     </row>
     <row r="504">
       <c r="A504" t="inlineStr">
@@ -52894,13 +52390,6 @@
           <t>[(24000, 10737975, 14561550), (23000, 9593175, 11840175), (24400, 8733900, 17632800)]</t>
         </is>
       </c>
-      <c r="AB504" t="inlineStr"/>
-      <c r="AC504" t="inlineStr"/>
-      <c r="AD504" t="inlineStr"/>
-      <c r="AE504" t="inlineStr"/>
-      <c r="AF504" t="inlineStr"/>
-      <c r="AG504" t="inlineStr"/>
-      <c r="AH504" t="inlineStr"/>
       <c r="AI504" t="n">
         <v>24400</v>
       </c>
@@ -53019,13 +52508,6 @@
           <t>[(24000, 10737975, 14561550), (23000, 9593175, 11840175), (24400, 8733900, 17632800)]</t>
         </is>
       </c>
-      <c r="AB505" t="inlineStr"/>
-      <c r="AC505" t="inlineStr"/>
-      <c r="AD505" t="inlineStr"/>
-      <c r="AE505" t="inlineStr"/>
-      <c r="AF505" t="inlineStr"/>
-      <c r="AG505" t="inlineStr"/>
-      <c r="AH505" t="inlineStr"/>
       <c r="AI505" t="n">
         <v>24400</v>
       </c>
@@ -53144,18 +52626,6 @@
           <t>[(24000, 10737975, 14561550), (23000, 9593175, 11840175), (24400, 8733900, 17632800)]</t>
         </is>
       </c>
-      <c r="AB506" t="inlineStr"/>
-      <c r="AC506" t="inlineStr"/>
-      <c r="AD506" t="inlineStr"/>
-      <c r="AE506" t="inlineStr"/>
-      <c r="AF506" t="inlineStr"/>
-      <c r="AG506" t="inlineStr"/>
-      <c r="AH506" t="inlineStr"/>
-      <c r="AI506" t="inlineStr"/>
-      <c r="AJ506" t="inlineStr"/>
-      <c r="AK506" t="inlineStr"/>
-      <c r="AL506" t="inlineStr"/>
-      <c r="AM506" t="inlineStr"/>
     </row>
     <row r="507">
       <c r="A507" t="inlineStr">
@@ -53259,17 +52729,11 @@
           <t>[(24000, 10737975, 14561550), (23000, 9593175, 11840175), (24400, 8733900, 17632800)]</t>
         </is>
       </c>
-      <c r="AB507" t="inlineStr"/>
       <c r="AC507" t="inlineStr">
         <is>
           <t>BREAKDOWN</t>
         </is>
       </c>
-      <c r="AD507" t="inlineStr"/>
-      <c r="AE507" t="inlineStr"/>
-      <c r="AF507" t="inlineStr"/>
-      <c r="AG507" t="inlineStr"/>
-      <c r="AH507" t="inlineStr"/>
       <c r="AI507" t="n">
         <v>24400</v>
       </c>
@@ -53388,18 +52852,6 @@
           <t>[(24000, 10703550, 14535375), (23000, 9517650, 11764200), (24400, 8585475, 17742600)]</t>
         </is>
       </c>
-      <c r="AB508" t="inlineStr"/>
-      <c r="AC508" t="inlineStr"/>
-      <c r="AD508" t="inlineStr"/>
-      <c r="AE508" t="inlineStr"/>
-      <c r="AF508" t="inlineStr"/>
-      <c r="AG508" t="inlineStr"/>
-      <c r="AH508" t="inlineStr"/>
-      <c r="AI508" t="inlineStr"/>
-      <c r="AJ508" t="inlineStr"/>
-      <c r="AK508" t="inlineStr"/>
-      <c r="AL508" t="inlineStr"/>
-      <c r="AM508" t="inlineStr"/>
     </row>
     <row r="509">
       <c r="A509" t="inlineStr">
@@ -53503,18 +52955,6 @@
           <t>[(24000, 10703550, 14535375), (23000, 9517650, 11764200), (24400, 8585475, 17742600)]</t>
         </is>
       </c>
-      <c r="AB509" t="inlineStr"/>
-      <c r="AC509" t="inlineStr"/>
-      <c r="AD509" t="inlineStr"/>
-      <c r="AE509" t="inlineStr"/>
-      <c r="AF509" t="inlineStr"/>
-      <c r="AG509" t="inlineStr"/>
-      <c r="AH509" t="inlineStr"/>
-      <c r="AI509" t="inlineStr"/>
-      <c r="AJ509" t="inlineStr"/>
-      <c r="AK509" t="inlineStr"/>
-      <c r="AL509" t="inlineStr"/>
-      <c r="AM509" t="inlineStr"/>
     </row>
     <row r="510">
       <c r="A510" t="inlineStr">
@@ -53618,18 +53058,6 @@
           <t>[(24000, 10698225, 14532000), (23000, 9486225, 11732775), (24400, 8505600, 17785500)]</t>
         </is>
       </c>
-      <c r="AB510" t="inlineStr"/>
-      <c r="AC510" t="inlineStr"/>
-      <c r="AD510" t="inlineStr"/>
-      <c r="AE510" t="inlineStr"/>
-      <c r="AF510" t="inlineStr"/>
-      <c r="AG510" t="inlineStr"/>
-      <c r="AH510" t="inlineStr"/>
-      <c r="AI510" t="inlineStr"/>
-      <c r="AJ510" t="inlineStr"/>
-      <c r="AK510" t="inlineStr"/>
-      <c r="AL510" t="inlineStr"/>
-      <c r="AM510" t="inlineStr"/>
     </row>
     <row r="511">
       <c r="A511" t="inlineStr">
@@ -53733,18 +53161,6 @@
           <t>[(24000, 10698225, 14532000), (23000, 9486225, 11732925), (24400, 8505600, 17785500)]</t>
         </is>
       </c>
-      <c r="AB511" t="inlineStr"/>
-      <c r="AC511" t="inlineStr"/>
-      <c r="AD511" t="inlineStr"/>
-      <c r="AE511" t="inlineStr"/>
-      <c r="AF511" t="inlineStr"/>
-      <c r="AG511" t="inlineStr"/>
-      <c r="AH511" t="inlineStr"/>
-      <c r="AI511" t="inlineStr"/>
-      <c r="AJ511" t="inlineStr"/>
-      <c r="AK511" t="inlineStr"/>
-      <c r="AL511" t="inlineStr"/>
-      <c r="AM511" t="inlineStr"/>
     </row>
     <row r="512">
       <c r="A512" t="inlineStr">
@@ -53848,18 +53264,6 @@
           <t>[(24000, 10698225, 14532000), (23000, 9486225, 11732925), (24400, 8505600, 17785500)]</t>
         </is>
       </c>
-      <c r="AB512" t="inlineStr"/>
-      <c r="AC512" t="inlineStr"/>
-      <c r="AD512" t="inlineStr"/>
-      <c r="AE512" t="inlineStr"/>
-      <c r="AF512" t="inlineStr"/>
-      <c r="AG512" t="inlineStr"/>
-      <c r="AH512" t="inlineStr"/>
-      <c r="AI512" t="inlineStr"/>
-      <c r="AJ512" t="inlineStr"/>
-      <c r="AK512" t="inlineStr"/>
-      <c r="AL512" t="inlineStr"/>
-      <c r="AM512" t="inlineStr"/>
     </row>
     <row r="513">
       <c r="A513" t="inlineStr">
@@ -53963,18 +53367,6 @@
           <t>[(24000, 10694175, 14526525), (23000, 9478275, 11724975), (24400, 8577525, 17877450)]</t>
         </is>
       </c>
-      <c r="AB513" t="inlineStr"/>
-      <c r="AC513" t="inlineStr"/>
-      <c r="AD513" t="inlineStr"/>
-      <c r="AE513" t="inlineStr"/>
-      <c r="AF513" t="inlineStr"/>
-      <c r="AG513" t="inlineStr"/>
-      <c r="AH513" t="inlineStr"/>
-      <c r="AI513" t="inlineStr"/>
-      <c r="AJ513" t="inlineStr"/>
-      <c r="AK513" t="inlineStr"/>
-      <c r="AL513" t="inlineStr"/>
-      <c r="AM513" t="inlineStr"/>
     </row>
     <row r="514">
       <c r="A514" t="inlineStr">
@@ -54078,18 +53470,6 @@
           <t>[(24000, 10694175, 14526525), (23000, 9478275, 11724975), (24400, 8577525, 17877450)]</t>
         </is>
       </c>
-      <c r="AB514" t="inlineStr"/>
-      <c r="AC514" t="inlineStr"/>
-      <c r="AD514" t="inlineStr"/>
-      <c r="AE514" t="inlineStr"/>
-      <c r="AF514" t="inlineStr"/>
-      <c r="AG514" t="inlineStr"/>
-      <c r="AH514" t="inlineStr"/>
-      <c r="AI514" t="inlineStr"/>
-      <c r="AJ514" t="inlineStr"/>
-      <c r="AK514" t="inlineStr"/>
-      <c r="AL514" t="inlineStr"/>
-      <c r="AM514" t="inlineStr"/>
     </row>
     <row r="515">
       <c r="A515" t="inlineStr">
@@ -54193,18 +53573,6 @@
           <t>[(24000, 10694175, 14526525), (23000, 9478275, 11725050), (24400, 8577525, 17877450)]</t>
         </is>
       </c>
-      <c r="AB515" t="inlineStr"/>
-      <c r="AC515" t="inlineStr"/>
-      <c r="AD515" t="inlineStr"/>
-      <c r="AE515" t="inlineStr"/>
-      <c r="AF515" t="inlineStr"/>
-      <c r="AG515" t="inlineStr"/>
-      <c r="AH515" t="inlineStr"/>
-      <c r="AI515" t="inlineStr"/>
-      <c r="AJ515" t="inlineStr"/>
-      <c r="AK515" t="inlineStr"/>
-      <c r="AL515" t="inlineStr"/>
-      <c r="AM515" t="inlineStr"/>
     </row>
     <row r="516">
       <c r="A516" t="inlineStr">
@@ -54308,18 +53676,6 @@
           <t>[(24000, 10697700, 14528325), (23000, 9547650, 11794425), (24400, 8741625, 17956875)]</t>
         </is>
       </c>
-      <c r="AB516" t="inlineStr"/>
-      <c r="AC516" t="inlineStr"/>
-      <c r="AD516" t="inlineStr"/>
-      <c r="AE516" t="inlineStr"/>
-      <c r="AF516" t="inlineStr"/>
-      <c r="AG516" t="inlineStr"/>
-      <c r="AH516" t="inlineStr"/>
-      <c r="AI516" t="inlineStr"/>
-      <c r="AJ516" t="inlineStr"/>
-      <c r="AK516" t="inlineStr"/>
-      <c r="AL516" t="inlineStr"/>
-      <c r="AM516" t="inlineStr"/>
     </row>
     <row r="517">
       <c r="A517" t="inlineStr">
@@ -54423,18 +53779,6 @@
           <t>[(24000, 10697700, 14528325), (23000, 9547650, 11794275), (24400, 8741625, 17956875)]</t>
         </is>
       </c>
-      <c r="AB517" t="inlineStr"/>
-      <c r="AC517" t="inlineStr"/>
-      <c r="AD517" t="inlineStr"/>
-      <c r="AE517" t="inlineStr"/>
-      <c r="AF517" t="inlineStr"/>
-      <c r="AG517" t="inlineStr"/>
-      <c r="AH517" t="inlineStr"/>
-      <c r="AI517" t="inlineStr"/>
-      <c r="AJ517" t="inlineStr"/>
-      <c r="AK517" t="inlineStr"/>
-      <c r="AL517" t="inlineStr"/>
-      <c r="AM517" t="inlineStr"/>
     </row>
     <row r="518">
       <c r="A518" t="inlineStr">
@@ -54538,18 +53882,6 @@
           <t>[(24000, 10697700, 14528325), (23000, 9547650, 11794275), (24400, 8741625, 17956875)]</t>
         </is>
       </c>
-      <c r="AB518" t="inlineStr"/>
-      <c r="AC518" t="inlineStr"/>
-      <c r="AD518" t="inlineStr"/>
-      <c r="AE518" t="inlineStr"/>
-      <c r="AF518" t="inlineStr"/>
-      <c r="AG518" t="inlineStr"/>
-      <c r="AH518" t="inlineStr"/>
-      <c r="AI518" t="inlineStr"/>
-      <c r="AJ518" t="inlineStr"/>
-      <c r="AK518" t="inlineStr"/>
-      <c r="AL518" t="inlineStr"/>
-      <c r="AM518" t="inlineStr"/>
     </row>
     <row r="519">
       <c r="A519" t="inlineStr">
@@ -54653,18 +53985,6 @@
           <t>[(24000, 10603950, 14325600), (23000, 9541350, 11787975), (24400, 8836350, 18094875)]</t>
         </is>
       </c>
-      <c r="AB519" t="inlineStr"/>
-      <c r="AC519" t="inlineStr"/>
-      <c r="AD519" t="inlineStr"/>
-      <c r="AE519" t="inlineStr"/>
-      <c r="AF519" t="inlineStr"/>
-      <c r="AG519" t="inlineStr"/>
-      <c r="AH519" t="inlineStr"/>
-      <c r="AI519" t="inlineStr"/>
-      <c r="AJ519" t="inlineStr"/>
-      <c r="AK519" t="inlineStr"/>
-      <c r="AL519" t="inlineStr"/>
-      <c r="AM519" t="inlineStr"/>
     </row>
     <row r="520">
       <c r="A520" t="inlineStr">
@@ -54768,18 +54088,6 @@
           <t>[(24000, 10603950, 14325600), (23000, 9541350, 11787975), (24400, 8836350, 18094875)]</t>
         </is>
       </c>
-      <c r="AB520" t="inlineStr"/>
-      <c r="AC520" t="inlineStr"/>
-      <c r="AD520" t="inlineStr"/>
-      <c r="AE520" t="inlineStr"/>
-      <c r="AF520" t="inlineStr"/>
-      <c r="AG520" t="inlineStr"/>
-      <c r="AH520" t="inlineStr"/>
-      <c r="AI520" t="inlineStr"/>
-      <c r="AJ520" t="inlineStr"/>
-      <c r="AK520" t="inlineStr"/>
-      <c r="AL520" t="inlineStr"/>
-      <c r="AM520" t="inlineStr"/>
     </row>
     <row r="521">
       <c r="A521" t="inlineStr">
@@ -54883,18 +54191,6 @@
           <t>[(24000, 10603950, 14325600), (23000, 9541350, 11787975), (24400, 8836350, 18094875)]</t>
         </is>
       </c>
-      <c r="AB521" t="inlineStr"/>
-      <c r="AC521" t="inlineStr"/>
-      <c r="AD521" t="inlineStr"/>
-      <c r="AE521" t="inlineStr"/>
-      <c r="AF521" t="inlineStr"/>
-      <c r="AG521" t="inlineStr"/>
-      <c r="AH521" t="inlineStr"/>
-      <c r="AI521" t="inlineStr"/>
-      <c r="AJ521" t="inlineStr"/>
-      <c r="AK521" t="inlineStr"/>
-      <c r="AL521" t="inlineStr"/>
-      <c r="AM521" t="inlineStr"/>
     </row>
     <row r="522">
       <c r="A522" t="inlineStr">
@@ -54998,18 +54294,6 @@
           <t>[(24000, 10675200, 14396325), (23000, 9512025, 11758650), (24400, 8863050, 18028575)]</t>
         </is>
       </c>
-      <c r="AB522" t="inlineStr"/>
-      <c r="AC522" t="inlineStr"/>
-      <c r="AD522" t="inlineStr"/>
-      <c r="AE522" t="inlineStr"/>
-      <c r="AF522" t="inlineStr"/>
-      <c r="AG522" t="inlineStr"/>
-      <c r="AH522" t="inlineStr"/>
-      <c r="AI522" t="inlineStr"/>
-      <c r="AJ522" t="inlineStr"/>
-      <c r="AK522" t="inlineStr"/>
-      <c r="AL522" t="inlineStr"/>
-      <c r="AM522" t="inlineStr"/>
     </row>
     <row r="523">
       <c r="A523" t="inlineStr">
@@ -55113,18 +54397,6 @@
           <t>[(24000, 10675200, 14396325), (23000, 9512025, 11758650), (24400, 8863050, 18028575)]</t>
         </is>
       </c>
-      <c r="AB523" t="inlineStr"/>
-      <c r="AC523" t="inlineStr"/>
-      <c r="AD523" t="inlineStr"/>
-      <c r="AE523" t="inlineStr"/>
-      <c r="AF523" t="inlineStr"/>
-      <c r="AG523" t="inlineStr"/>
-      <c r="AH523" t="inlineStr"/>
-      <c r="AI523" t="inlineStr"/>
-      <c r="AJ523" t="inlineStr"/>
-      <c r="AK523" t="inlineStr"/>
-      <c r="AL523" t="inlineStr"/>
-      <c r="AM523" t="inlineStr"/>
     </row>
     <row r="524">
       <c r="A524" t="inlineStr">
@@ -55228,18 +54500,6 @@
           <t>[(24000, 10675200, 14396325), (23000, 9512025, 11758650), (24400, 8863050, 18028575)]</t>
         </is>
       </c>
-      <c r="AB524" t="inlineStr"/>
-      <c r="AC524" t="inlineStr"/>
-      <c r="AD524" t="inlineStr"/>
-      <c r="AE524" t="inlineStr"/>
-      <c r="AF524" t="inlineStr"/>
-      <c r="AG524" t="inlineStr"/>
-      <c r="AH524" t="inlineStr"/>
-      <c r="AI524" t="inlineStr"/>
-      <c r="AJ524" t="inlineStr"/>
-      <c r="AK524" t="inlineStr"/>
-      <c r="AL524" t="inlineStr"/>
-      <c r="AM524" t="inlineStr"/>
     </row>
     <row r="525">
       <c r="A525" t="inlineStr">
@@ -55343,18 +54603,6 @@
           <t>[(24000, 10610025, 14327700), (23000, 9489675, 11736150), (24400, 8673525, 17685675)]</t>
         </is>
       </c>
-      <c r="AB525" t="inlineStr"/>
-      <c r="AC525" t="inlineStr"/>
-      <c r="AD525" t="inlineStr"/>
-      <c r="AE525" t="inlineStr"/>
-      <c r="AF525" t="inlineStr"/>
-      <c r="AG525" t="inlineStr"/>
-      <c r="AH525" t="inlineStr"/>
-      <c r="AI525" t="inlineStr"/>
-      <c r="AJ525" t="inlineStr"/>
-      <c r="AK525" t="inlineStr"/>
-      <c r="AL525" t="inlineStr"/>
-      <c r="AM525" t="inlineStr"/>
     </row>
     <row r="526">
       <c r="A526" t="inlineStr">
@@ -55458,18 +54706,6 @@
           <t>[(24000, 10610025, 14327700), (23000, 9489675, 11736150), (24400, 8673525, 17685675)]</t>
         </is>
       </c>
-      <c r="AB526" t="inlineStr"/>
-      <c r="AC526" t="inlineStr"/>
-      <c r="AD526" t="inlineStr"/>
-      <c r="AE526" t="inlineStr"/>
-      <c r="AF526" t="inlineStr"/>
-      <c r="AG526" t="inlineStr"/>
-      <c r="AH526" t="inlineStr"/>
-      <c r="AI526" t="inlineStr"/>
-      <c r="AJ526" t="inlineStr"/>
-      <c r="AK526" t="inlineStr"/>
-      <c r="AL526" t="inlineStr"/>
-      <c r="AM526" t="inlineStr"/>
     </row>
     <row r="527">
       <c r="A527" t="inlineStr">
@@ -55573,18 +54809,6 @@
           <t>[(24000, 10610025, 14327700), (23000, 9489675, 11736150), (24400, 8673525, 17685675)]</t>
         </is>
       </c>
-      <c r="AB527" t="inlineStr"/>
-      <c r="AC527" t="inlineStr"/>
-      <c r="AD527" t="inlineStr"/>
-      <c r="AE527" t="inlineStr"/>
-      <c r="AF527" t="inlineStr"/>
-      <c r="AG527" t="inlineStr"/>
-      <c r="AH527" t="inlineStr"/>
-      <c r="AI527" t="inlineStr"/>
-      <c r="AJ527" t="inlineStr"/>
-      <c r="AK527" t="inlineStr"/>
-      <c r="AL527" t="inlineStr"/>
-      <c r="AM527" t="inlineStr"/>
     </row>
     <row r="528">
       <c r="A528" t="inlineStr">
@@ -55688,18 +54912,6 @@
           <t>[(24000, 10599150, 14315700), (23000, 9488025, 11734500), (24400, 8736675, 17648550)]</t>
         </is>
       </c>
-      <c r="AB528" t="inlineStr"/>
-      <c r="AC528" t="inlineStr"/>
-      <c r="AD528" t="inlineStr"/>
-      <c r="AE528" t="inlineStr"/>
-      <c r="AF528" t="inlineStr"/>
-      <c r="AG528" t="inlineStr"/>
-      <c r="AH528" t="inlineStr"/>
-      <c r="AI528" t="inlineStr"/>
-      <c r="AJ528" t="inlineStr"/>
-      <c r="AK528" t="inlineStr"/>
-      <c r="AL528" t="inlineStr"/>
-      <c r="AM528" t="inlineStr"/>
     </row>
     <row r="529">
       <c r="A529" t="inlineStr">
@@ -55803,18 +55015,6 @@
           <t>[(24000, 10599150, 14315700), (23000, 9488025, 11733225), (24400, 8736675, 17648550)]</t>
         </is>
       </c>
-      <c r="AB529" t="inlineStr"/>
-      <c r="AC529" t="inlineStr"/>
-      <c r="AD529" t="inlineStr"/>
-      <c r="AE529" t="inlineStr"/>
-      <c r="AF529" t="inlineStr"/>
-      <c r="AG529" t="inlineStr"/>
-      <c r="AH529" t="inlineStr"/>
-      <c r="AI529" t="inlineStr"/>
-      <c r="AJ529" t="inlineStr"/>
-      <c r="AK529" t="inlineStr"/>
-      <c r="AL529" t="inlineStr"/>
-      <c r="AM529" t="inlineStr"/>
     </row>
     <row r="530">
       <c r="A530" t="inlineStr">
@@ -55918,18 +55118,6 @@
           <t>[(24000, 10587825, 14301600), (23000, 9486750, 11731950), (24400, 8693850, 17641200)]</t>
         </is>
       </c>
-      <c r="AB530" t="inlineStr"/>
-      <c r="AC530" t="inlineStr"/>
-      <c r="AD530" t="inlineStr"/>
-      <c r="AE530" t="inlineStr"/>
-      <c r="AF530" t="inlineStr"/>
-      <c r="AG530" t="inlineStr"/>
-      <c r="AH530" t="inlineStr"/>
-      <c r="AI530" t="inlineStr"/>
-      <c r="AJ530" t="inlineStr"/>
-      <c r="AK530" t="inlineStr"/>
-      <c r="AL530" t="inlineStr"/>
-      <c r="AM530" t="inlineStr"/>
     </row>
     <row r="531">
       <c r="A531" t="inlineStr">
@@ -56033,18 +55221,6 @@
           <t>[(24000, 10587825, 14301600), (23000, 9486750, 11731425), (24400, 8693850, 17641200)]</t>
         </is>
       </c>
-      <c r="AB531" t="inlineStr"/>
-      <c r="AC531" t="inlineStr"/>
-      <c r="AD531" t="inlineStr"/>
-      <c r="AE531" t="inlineStr"/>
-      <c r="AF531" t="inlineStr"/>
-      <c r="AG531" t="inlineStr"/>
-      <c r="AH531" t="inlineStr"/>
-      <c r="AI531" t="inlineStr"/>
-      <c r="AJ531" t="inlineStr"/>
-      <c r="AK531" t="inlineStr"/>
-      <c r="AL531" t="inlineStr"/>
-      <c r="AM531" t="inlineStr"/>
     </row>
     <row r="532">
       <c r="A532" t="inlineStr">
@@ -56148,18 +55324,6 @@
           <t>[(24000, 10607325, 14313225), (23000, 9495225, 11739900), (22000, 8733975, 9749700)]</t>
         </is>
       </c>
-      <c r="AB532" t="inlineStr"/>
-      <c r="AC532" t="inlineStr"/>
-      <c r="AD532" t="inlineStr"/>
-      <c r="AE532" t="inlineStr"/>
-      <c r="AF532" t="inlineStr"/>
-      <c r="AG532" t="inlineStr"/>
-      <c r="AH532" t="inlineStr"/>
-      <c r="AI532" t="inlineStr"/>
-      <c r="AJ532" t="inlineStr"/>
-      <c r="AK532" t="inlineStr"/>
-      <c r="AL532" t="inlineStr"/>
-      <c r="AM532" t="inlineStr"/>
     </row>
     <row r="533">
       <c r="A533" t="inlineStr">
@@ -56263,18 +55427,6 @@
           <t>[(24000, 10588350, 14294250), (23000, 9454500, 11699175), (22000, 8766375, 9782100)]</t>
         </is>
       </c>
-      <c r="AB533" t="inlineStr"/>
-      <c r="AC533" t="inlineStr"/>
-      <c r="AD533" t="inlineStr"/>
-      <c r="AE533" t="inlineStr"/>
-      <c r="AF533" t="inlineStr"/>
-      <c r="AG533" t="inlineStr"/>
-      <c r="AH533" t="inlineStr"/>
-      <c r="AI533" t="inlineStr"/>
-      <c r="AJ533" t="inlineStr"/>
-      <c r="AK533" t="inlineStr"/>
-      <c r="AL533" t="inlineStr"/>
-      <c r="AM533" t="inlineStr"/>
     </row>
     <row r="534">
       <c r="A534" t="inlineStr">
@@ -56378,18 +55530,6 @@
           <t>[(24000, 10588350, 14291250), (23000, 9454500, 11699100), (22000, 8766375, 9782100)]</t>
         </is>
       </c>
-      <c r="AB534" t="inlineStr"/>
-      <c r="AC534" t="inlineStr"/>
-      <c r="AD534" t="inlineStr"/>
-      <c r="AE534" t="inlineStr"/>
-      <c r="AF534" t="inlineStr"/>
-      <c r="AG534" t="inlineStr"/>
-      <c r="AH534" t="inlineStr"/>
-      <c r="AI534" t="inlineStr"/>
-      <c r="AJ534" t="inlineStr"/>
-      <c r="AK534" t="inlineStr"/>
-      <c r="AL534" t="inlineStr"/>
-      <c r="AM534" t="inlineStr"/>
     </row>
     <row r="535">
       <c r="A535" t="inlineStr">
@@ -56493,18 +55633,6 @@
           <t>[(24000, 10588350, 14291250), (23000, 9454500, 11699100), (22000, 8766375, 9782100)]</t>
         </is>
       </c>
-      <c r="AB535" t="inlineStr"/>
-      <c r="AC535" t="inlineStr"/>
-      <c r="AD535" t="inlineStr"/>
-      <c r="AE535" t="inlineStr"/>
-      <c r="AF535" t="inlineStr"/>
-      <c r="AG535" t="inlineStr"/>
-      <c r="AH535" t="inlineStr"/>
-      <c r="AI535" t="inlineStr"/>
-      <c r="AJ535" t="inlineStr"/>
-      <c r="AK535" t="inlineStr"/>
-      <c r="AL535" t="inlineStr"/>
-      <c r="AM535" t="inlineStr"/>
     </row>
     <row r="536">
       <c r="A536" t="inlineStr">
@@ -56608,18 +55736,6 @@
           <t>[(24000, 10573500, 14277750), (23000, 9423375, 11667975), (22000, 8756625, 9772350)]</t>
         </is>
       </c>
-      <c r="AB536" t="inlineStr"/>
-      <c r="AC536" t="inlineStr"/>
-      <c r="AD536" t="inlineStr"/>
-      <c r="AE536" t="inlineStr"/>
-      <c r="AF536" t="inlineStr"/>
-      <c r="AG536" t="inlineStr"/>
-      <c r="AH536" t="inlineStr"/>
-      <c r="AI536" t="inlineStr"/>
-      <c r="AJ536" t="inlineStr"/>
-      <c r="AK536" t="inlineStr"/>
-      <c r="AL536" t="inlineStr"/>
-      <c r="AM536" t="inlineStr"/>
     </row>
     <row r="537">
       <c r="A537" t="inlineStr">
@@ -56723,18 +55839,6 @@
           <t>[(24000, 10573500, 14277750), (23000, 9423375, 11667975), (22000, 8756625, 9772350)]</t>
         </is>
       </c>
-      <c r="AB537" t="inlineStr"/>
-      <c r="AC537" t="inlineStr"/>
-      <c r="AD537" t="inlineStr"/>
-      <c r="AE537" t="inlineStr"/>
-      <c r="AF537" t="inlineStr"/>
-      <c r="AG537" t="inlineStr"/>
-      <c r="AH537" t="inlineStr"/>
-      <c r="AI537" t="inlineStr"/>
-      <c r="AJ537" t="inlineStr"/>
-      <c r="AK537" t="inlineStr"/>
-      <c r="AL537" t="inlineStr"/>
-      <c r="AM537" t="inlineStr"/>
     </row>
     <row r="538">
       <c r="A538" t="inlineStr">
@@ -56838,18 +55942,6 @@
           <t>[(24000, 10573500, 14277750), (23000, 9423375, 11667975), (22000, 8756625, 9772350)]</t>
         </is>
       </c>
-      <c r="AB538" t="inlineStr"/>
-      <c r="AC538" t="inlineStr"/>
-      <c r="AD538" t="inlineStr"/>
-      <c r="AE538" t="inlineStr"/>
-      <c r="AF538" t="inlineStr"/>
-      <c r="AG538" t="inlineStr"/>
-      <c r="AH538" t="inlineStr"/>
-      <c r="AI538" t="inlineStr"/>
-      <c r="AJ538" t="inlineStr"/>
-      <c r="AK538" t="inlineStr"/>
-      <c r="AL538" t="inlineStr"/>
-      <c r="AM538" t="inlineStr"/>
     </row>
     <row r="539">
       <c r="A539" t="inlineStr">
@@ -56953,18 +56045,6 @@
           <t>[(24000, 10568175, 14268000), (23000, 9401775, 11646450), (22000, 8747400, 9763050)]</t>
         </is>
       </c>
-      <c r="AB539" t="inlineStr"/>
-      <c r="AC539" t="inlineStr"/>
-      <c r="AD539" t="inlineStr"/>
-      <c r="AE539" t="inlineStr"/>
-      <c r="AF539" t="inlineStr"/>
-      <c r="AG539" t="inlineStr"/>
-      <c r="AH539" t="inlineStr"/>
-      <c r="AI539" t="inlineStr"/>
-      <c r="AJ539" t="inlineStr"/>
-      <c r="AK539" t="inlineStr"/>
-      <c r="AL539" t="inlineStr"/>
-      <c r="AM539" t="inlineStr"/>
     </row>
     <row r="540">
       <c r="A540" t="inlineStr">
@@ -57068,18 +56148,6 @@
           <t>[(24000, 10568175, 14268000), (23000, 9401775, 11646450), (22000, 8747400, 9763050)]</t>
         </is>
       </c>
-      <c r="AB540" t="inlineStr"/>
-      <c r="AC540" t="inlineStr"/>
-      <c r="AD540" t="inlineStr"/>
-      <c r="AE540" t="inlineStr"/>
-      <c r="AF540" t="inlineStr"/>
-      <c r="AG540" t="inlineStr"/>
-      <c r="AH540" t="inlineStr"/>
-      <c r="AI540" t="inlineStr"/>
-      <c r="AJ540" t="inlineStr"/>
-      <c r="AK540" t="inlineStr"/>
-      <c r="AL540" t="inlineStr"/>
-      <c r="AM540" t="inlineStr"/>
     </row>
     <row r="541">
       <c r="A541" t="inlineStr">
@@ -57183,18 +56251,6 @@
           <t>[(24000, 10568175, 14268000), (23000, 9401775, 11646450), (22000, 8747400, 9763050)]</t>
         </is>
       </c>
-      <c r="AB541" t="inlineStr"/>
-      <c r="AC541" t="inlineStr"/>
-      <c r="AD541" t="inlineStr"/>
-      <c r="AE541" t="inlineStr"/>
-      <c r="AF541" t="inlineStr"/>
-      <c r="AG541" t="inlineStr"/>
-      <c r="AH541" t="inlineStr"/>
-      <c r="AI541" t="inlineStr"/>
-      <c r="AJ541" t="inlineStr"/>
-      <c r="AK541" t="inlineStr"/>
-      <c r="AL541" t="inlineStr"/>
-      <c r="AM541" t="inlineStr"/>
     </row>
     <row r="542">
       <c r="A542" t="inlineStr">
@@ -57298,18 +56354,6 @@
           <t>[(24000, 10570725, 14268150), (23000, 9414000, 11658225), (22000, 8737725, 9753375)]</t>
         </is>
       </c>
-      <c r="AB542" t="inlineStr"/>
-      <c r="AC542" t="inlineStr"/>
-      <c r="AD542" t="inlineStr"/>
-      <c r="AE542" t="inlineStr"/>
-      <c r="AF542" t="inlineStr"/>
-      <c r="AG542" t="inlineStr"/>
-      <c r="AH542" t="inlineStr"/>
-      <c r="AI542" t="inlineStr"/>
-      <c r="AJ542" t="inlineStr"/>
-      <c r="AK542" t="inlineStr"/>
-      <c r="AL542" t="inlineStr"/>
-      <c r="AM542" t="inlineStr"/>
     </row>
     <row r="543">
       <c r="A543" t="inlineStr">
@@ -57413,18 +56457,6 @@
           <t>[(24000, 10570725, 14268150), (23000, 9414000, 11658225), (22000, 8737725, 9753375)]</t>
         </is>
       </c>
-      <c r="AB543" t="inlineStr"/>
-      <c r="AC543" t="inlineStr"/>
-      <c r="AD543" t="inlineStr"/>
-      <c r="AE543" t="inlineStr"/>
-      <c r="AF543" t="inlineStr"/>
-      <c r="AG543" t="inlineStr"/>
-      <c r="AH543" t="inlineStr"/>
-      <c r="AI543" t="inlineStr"/>
-      <c r="AJ543" t="inlineStr"/>
-      <c r="AK543" t="inlineStr"/>
-      <c r="AL543" t="inlineStr"/>
-      <c r="AM543" t="inlineStr"/>
     </row>
     <row r="544">
       <c r="A544" t="inlineStr">
@@ -57528,18 +56560,6 @@
           <t>[(24000, 10570725, 14268150), (23000, 9414000, 11658225), (22000, 8737725, 9753375)]</t>
         </is>
       </c>
-      <c r="AB544" t="inlineStr"/>
-      <c r="AC544" t="inlineStr"/>
-      <c r="AD544" t="inlineStr"/>
-      <c r="AE544" t="inlineStr"/>
-      <c r="AF544" t="inlineStr"/>
-      <c r="AG544" t="inlineStr"/>
-      <c r="AH544" t="inlineStr"/>
-      <c r="AI544" t="inlineStr"/>
-      <c r="AJ544" t="inlineStr"/>
-      <c r="AK544" t="inlineStr"/>
-      <c r="AL544" t="inlineStr"/>
-      <c r="AM544" t="inlineStr"/>
     </row>
     <row r="545">
       <c r="A545" t="inlineStr">
@@ -57643,18 +56663,6 @@
           <t>[(24000, 10564575, 14260425), (23000, 9368550, 11612775), (22000, 8806800, 9822450)]</t>
         </is>
       </c>
-      <c r="AB545" t="inlineStr"/>
-      <c r="AC545" t="inlineStr"/>
-      <c r="AD545" t="inlineStr"/>
-      <c r="AE545" t="inlineStr"/>
-      <c r="AF545" t="inlineStr"/>
-      <c r="AG545" t="inlineStr"/>
-      <c r="AH545" t="inlineStr"/>
-      <c r="AI545" t="inlineStr"/>
-      <c r="AJ545" t="inlineStr"/>
-      <c r="AK545" t="inlineStr"/>
-      <c r="AL545" t="inlineStr"/>
-      <c r="AM545" t="inlineStr"/>
     </row>
     <row r="546">
       <c r="A546" t="inlineStr">
@@ -57758,18 +56766,6 @@
           <t>[(24000, 10564575, 14260425), (23000, 9368550, 11612775), (22000, 8806800, 9822450)]</t>
         </is>
       </c>
-      <c r="AB546" t="inlineStr"/>
-      <c r="AC546" t="inlineStr"/>
-      <c r="AD546" t="inlineStr"/>
-      <c r="AE546" t="inlineStr"/>
-      <c r="AF546" t="inlineStr"/>
-      <c r="AG546" t="inlineStr"/>
-      <c r="AH546" t="inlineStr"/>
-      <c r="AI546" t="inlineStr"/>
-      <c r="AJ546" t="inlineStr"/>
-      <c r="AK546" t="inlineStr"/>
-      <c r="AL546" t="inlineStr"/>
-      <c r="AM546" t="inlineStr"/>
     </row>
     <row r="547">
       <c r="A547" t="inlineStr">
@@ -57873,18 +56869,6 @@
           <t>[(24000, 10564575, 14260425), (23000, 9368550, 11612775), (22000, 8806800, 9822450)]</t>
         </is>
       </c>
-      <c r="AB547" t="inlineStr"/>
-      <c r="AC547" t="inlineStr"/>
-      <c r="AD547" t="inlineStr"/>
-      <c r="AE547" t="inlineStr"/>
-      <c r="AF547" t="inlineStr"/>
-      <c r="AG547" t="inlineStr"/>
-      <c r="AH547" t="inlineStr"/>
-      <c r="AI547" t="inlineStr"/>
-      <c r="AJ547" t="inlineStr"/>
-      <c r="AK547" t="inlineStr"/>
-      <c r="AL547" t="inlineStr"/>
-      <c r="AM547" t="inlineStr"/>
     </row>
     <row r="548">
       <c r="A548" t="inlineStr">
@@ -57988,18 +56972,6 @@
           <t>[(24000, 10512000, 14208375), (23000, 9277575, 11521800), (22000, 8803050, 9819150)]</t>
         </is>
       </c>
-      <c r="AB548" t="inlineStr"/>
-      <c r="AC548" t="inlineStr"/>
-      <c r="AD548" t="inlineStr"/>
-      <c r="AE548" t="inlineStr"/>
-      <c r="AF548" t="inlineStr"/>
-      <c r="AG548" t="inlineStr"/>
-      <c r="AH548" t="inlineStr"/>
-      <c r="AI548" t="inlineStr"/>
-      <c r="AJ548" t="inlineStr"/>
-      <c r="AK548" t="inlineStr"/>
-      <c r="AL548" t="inlineStr"/>
-      <c r="AM548" t="inlineStr"/>
     </row>
     <row r="549">
       <c r="A549" t="inlineStr">
@@ -58103,18 +57075,6 @@
           <t>[(24000, 10512000, 14208375), (23000, 9277575, 11521800), (22000, 8803050, 9819150)]</t>
         </is>
       </c>
-      <c r="AB549" t="inlineStr"/>
-      <c r="AC549" t="inlineStr"/>
-      <c r="AD549" t="inlineStr"/>
-      <c r="AE549" t="inlineStr"/>
-      <c r="AF549" t="inlineStr"/>
-      <c r="AG549" t="inlineStr"/>
-      <c r="AH549" t="inlineStr"/>
-      <c r="AI549" t="inlineStr"/>
-      <c r="AJ549" t="inlineStr"/>
-      <c r="AK549" t="inlineStr"/>
-      <c r="AL549" t="inlineStr"/>
-      <c r="AM549" t="inlineStr"/>
     </row>
     <row r="550">
       <c r="A550" t="inlineStr">
@@ -58218,18 +57178,6 @@
           <t>[(24000, 10512000, 14208375), (23000, 9277575, 11522025), (22000, 8803050, 9819150)]</t>
         </is>
       </c>
-      <c r="AB550" t="inlineStr"/>
-      <c r="AC550" t="inlineStr"/>
-      <c r="AD550" t="inlineStr"/>
-      <c r="AE550" t="inlineStr"/>
-      <c r="AF550" t="inlineStr"/>
-      <c r="AG550" t="inlineStr"/>
-      <c r="AH550" t="inlineStr"/>
-      <c r="AI550" t="inlineStr"/>
-      <c r="AJ550" t="inlineStr"/>
-      <c r="AK550" t="inlineStr"/>
-      <c r="AL550" t="inlineStr"/>
-      <c r="AM550" t="inlineStr"/>
     </row>
     <row r="551">
       <c r="A551" t="inlineStr">
@@ -58333,18 +57281,6 @@
           <t>[(24000, 10464525, 14169675), (23000, 9287250, 11531700), (22000, 8740350, 9756450)]</t>
         </is>
       </c>
-      <c r="AB551" t="inlineStr"/>
-      <c r="AC551" t="inlineStr"/>
-      <c r="AD551" t="inlineStr"/>
-      <c r="AE551" t="inlineStr"/>
-      <c r="AF551" t="inlineStr"/>
-      <c r="AG551" t="inlineStr"/>
-      <c r="AH551" t="inlineStr"/>
-      <c r="AI551" t="inlineStr"/>
-      <c r="AJ551" t="inlineStr"/>
-      <c r="AK551" t="inlineStr"/>
-      <c r="AL551" t="inlineStr"/>
-      <c r="AM551" t="inlineStr"/>
     </row>
     <row r="552">
       <c r="A552" t="inlineStr">
@@ -58448,18 +57384,6 @@
           <t>[(24000, 10464525, 14169675), (23000, 9287250, 11531700), (22000, 8740350, 9756450)]</t>
         </is>
       </c>
-      <c r="AB552" t="inlineStr"/>
-      <c r="AC552" t="inlineStr"/>
-      <c r="AD552" t="inlineStr"/>
-      <c r="AE552" t="inlineStr"/>
-      <c r="AF552" t="inlineStr"/>
-      <c r="AG552" t="inlineStr"/>
-      <c r="AH552" t="inlineStr"/>
-      <c r="AI552" t="inlineStr"/>
-      <c r="AJ552" t="inlineStr"/>
-      <c r="AK552" t="inlineStr"/>
-      <c r="AL552" t="inlineStr"/>
-      <c r="AM552" t="inlineStr"/>
     </row>
     <row r="553">
       <c r="A553" t="inlineStr">
@@ -58563,18 +57487,6 @@
           <t>[(24000, 10464525, 14169675), (23000, 9287250, 11531850), (22000, 8740350, 9756375)]</t>
         </is>
       </c>
-      <c r="AB553" t="inlineStr"/>
-      <c r="AC553" t="inlineStr"/>
-      <c r="AD553" t="inlineStr"/>
-      <c r="AE553" t="inlineStr"/>
-      <c r="AF553" t="inlineStr"/>
-      <c r="AG553" t="inlineStr"/>
-      <c r="AH553" t="inlineStr"/>
-      <c r="AI553" t="inlineStr"/>
-      <c r="AJ553" t="inlineStr"/>
-      <c r="AK553" t="inlineStr"/>
-      <c r="AL553" t="inlineStr"/>
-      <c r="AM553" t="inlineStr"/>
     </row>
     <row r="554">
       <c r="A554" t="inlineStr">
@@ -58678,18 +57590,6 @@
           <t>[(24000, 10375725, 14085750), (23000, 9324075, 11568675), (22000, 8760825, 9776850)]</t>
         </is>
       </c>
-      <c r="AB554" t="inlineStr"/>
-      <c r="AC554" t="inlineStr"/>
-      <c r="AD554" t="inlineStr"/>
-      <c r="AE554" t="inlineStr"/>
-      <c r="AF554" t="inlineStr"/>
-      <c r="AG554" t="inlineStr"/>
-      <c r="AH554" t="inlineStr"/>
-      <c r="AI554" t="inlineStr"/>
-      <c r="AJ554" t="inlineStr"/>
-      <c r="AK554" t="inlineStr"/>
-      <c r="AL554" t="inlineStr"/>
-      <c r="AM554" t="inlineStr"/>
     </row>
     <row r="555">
       <c r="A555" t="inlineStr">
@@ -58793,18 +57693,6 @@
           <t>[(24000, 10375725, 14085750), (23000, 9324075, 11568825), (22000, 8760825, 9776850)]</t>
         </is>
       </c>
-      <c r="AB555" t="inlineStr"/>
-      <c r="AC555" t="inlineStr"/>
-      <c r="AD555" t="inlineStr"/>
-      <c r="AE555" t="inlineStr"/>
-      <c r="AF555" t="inlineStr"/>
-      <c r="AG555" t="inlineStr"/>
-      <c r="AH555" t="inlineStr"/>
-      <c r="AI555" t="inlineStr"/>
-      <c r="AJ555" t="inlineStr"/>
-      <c r="AK555" t="inlineStr"/>
-      <c r="AL555" t="inlineStr"/>
-      <c r="AM555" t="inlineStr"/>
     </row>
     <row r="556">
       <c r="A556" t="inlineStr">
@@ -58908,18 +57796,6 @@
           <t>[(24000, 10375725, 14085750), (23000, 9324075, 11568825), (22000, 8760825, 9776850)]</t>
         </is>
       </c>
-      <c r="AB556" t="inlineStr"/>
-      <c r="AC556" t="inlineStr"/>
-      <c r="AD556" t="inlineStr"/>
-      <c r="AE556" t="inlineStr"/>
-      <c r="AF556" t="inlineStr"/>
-      <c r="AG556" t="inlineStr"/>
-      <c r="AH556" t="inlineStr"/>
-      <c r="AI556" t="inlineStr"/>
-      <c r="AJ556" t="inlineStr"/>
-      <c r="AK556" t="inlineStr"/>
-      <c r="AL556" t="inlineStr"/>
-      <c r="AM556" t="inlineStr"/>
     </row>
     <row r="557">
       <c r="A557" t="inlineStr">
@@ -59023,18 +57899,6 @@
           <t>[(24000, 10066575, 13766850), (23000, 9283875, 11528625), (22000, 8853750, 9869775)]</t>
         </is>
       </c>
-      <c r="AB557" t="inlineStr"/>
-      <c r="AC557" t="inlineStr"/>
-      <c r="AD557" t="inlineStr"/>
-      <c r="AE557" t="inlineStr"/>
-      <c r="AF557" t="inlineStr"/>
-      <c r="AG557" t="inlineStr"/>
-      <c r="AH557" t="inlineStr"/>
-      <c r="AI557" t="inlineStr"/>
-      <c r="AJ557" t="inlineStr"/>
-      <c r="AK557" t="inlineStr"/>
-      <c r="AL557" t="inlineStr"/>
-      <c r="AM557" t="inlineStr"/>
     </row>
     <row r="558">
       <c r="A558" t="inlineStr">
@@ -59138,18 +58002,6 @@
           <t>[(24000, 10066575, 13766850), (23000, 9283875, 11528775), (22000, 8853750, 9869775)]</t>
         </is>
       </c>
-      <c r="AB558" t="inlineStr"/>
-      <c r="AC558" t="inlineStr"/>
-      <c r="AD558" t="inlineStr"/>
-      <c r="AE558" t="inlineStr"/>
-      <c r="AF558" t="inlineStr"/>
-      <c r="AG558" t="inlineStr"/>
-      <c r="AH558" t="inlineStr"/>
-      <c r="AI558" t="inlineStr"/>
-      <c r="AJ558" t="inlineStr"/>
-      <c r="AK558" t="inlineStr"/>
-      <c r="AL558" t="inlineStr"/>
-      <c r="AM558" t="inlineStr"/>
     </row>
     <row r="559">
       <c r="A559" t="inlineStr">
@@ -59253,18 +58105,6 @@
           <t>[(24000, 10066575, 13766850), (23000, 9283875, 11528775), (22000, 8853750, 9869775)]</t>
         </is>
       </c>
-      <c r="AB559" t="inlineStr"/>
-      <c r="AC559" t="inlineStr"/>
-      <c r="AD559" t="inlineStr"/>
-      <c r="AE559" t="inlineStr"/>
-      <c r="AF559" t="inlineStr"/>
-      <c r="AG559" t="inlineStr"/>
-      <c r="AH559" t="inlineStr"/>
-      <c r="AI559" t="inlineStr"/>
-      <c r="AJ559" t="inlineStr"/>
-      <c r="AK559" t="inlineStr"/>
-      <c r="AL559" t="inlineStr"/>
-      <c r="AM559" t="inlineStr"/>
     </row>
     <row r="560">
       <c r="A560" t="inlineStr">
@@ -59368,18 +58208,6 @@
           <t>[(24000, 9951900, 13636200), (23000, 9226800, 11475825), (22000, 8833500, 9849525)]</t>
         </is>
       </c>
-      <c r="AB560" t="inlineStr"/>
-      <c r="AC560" t="inlineStr"/>
-      <c r="AD560" t="inlineStr"/>
-      <c r="AE560" t="inlineStr"/>
-      <c r="AF560" t="inlineStr"/>
-      <c r="AG560" t="inlineStr"/>
-      <c r="AH560" t="inlineStr"/>
-      <c r="AI560" t="inlineStr"/>
-      <c r="AJ560" t="inlineStr"/>
-      <c r="AK560" t="inlineStr"/>
-      <c r="AL560" t="inlineStr"/>
-      <c r="AM560" t="inlineStr"/>
     </row>
     <row r="561">
       <c r="A561" t="inlineStr">
@@ -59483,18 +58311,6 @@
           <t>[(24000, 9951900, 13636200), (23000, 9226800, 11475825), (22000, 8833500, 9849450)]</t>
         </is>
       </c>
-      <c r="AB561" t="inlineStr"/>
-      <c r="AC561" t="inlineStr"/>
-      <c r="AD561" t="inlineStr"/>
-      <c r="AE561" t="inlineStr"/>
-      <c r="AF561" t="inlineStr"/>
-      <c r="AG561" t="inlineStr"/>
-      <c r="AH561" t="inlineStr"/>
-      <c r="AI561" t="inlineStr"/>
-      <c r="AJ561" t="inlineStr"/>
-      <c r="AK561" t="inlineStr"/>
-      <c r="AL561" t="inlineStr"/>
-      <c r="AM561" t="inlineStr"/>
     </row>
     <row r="562">
       <c r="A562" t="inlineStr">
@@ -59598,18 +58414,6 @@
           <t>[(24000, 9951900, 13636200), (23000, 9226800, 11475825), (22000, 8833500, 9849450)]</t>
         </is>
       </c>
-      <c r="AB562" t="inlineStr"/>
-      <c r="AC562" t="inlineStr"/>
-      <c r="AD562" t="inlineStr"/>
-      <c r="AE562" t="inlineStr"/>
-      <c r="AF562" t="inlineStr"/>
-      <c r="AG562" t="inlineStr"/>
-      <c r="AH562" t="inlineStr"/>
-      <c r="AI562" t="inlineStr"/>
-      <c r="AJ562" t="inlineStr"/>
-      <c r="AK562" t="inlineStr"/>
-      <c r="AL562" t="inlineStr"/>
-      <c r="AM562" t="inlineStr"/>
     </row>
     <row r="563">
       <c r="A563" t="inlineStr">
@@ -59713,18 +58517,6 @@
           <t>[(24000, 9849675, 13529475), (23000, 9390450, 11639475), (22000, 8835000, 9850950)]</t>
         </is>
       </c>
-      <c r="AB563" t="inlineStr"/>
-      <c r="AC563" t="inlineStr"/>
-      <c r="AD563" t="inlineStr"/>
-      <c r="AE563" t="inlineStr"/>
-      <c r="AF563" t="inlineStr"/>
-      <c r="AG563" t="inlineStr"/>
-      <c r="AH563" t="inlineStr"/>
-      <c r="AI563" t="inlineStr"/>
-      <c r="AJ563" t="inlineStr"/>
-      <c r="AK563" t="inlineStr"/>
-      <c r="AL563" t="inlineStr"/>
-      <c r="AM563" t="inlineStr"/>
     </row>
     <row r="564">
       <c r="A564" t="inlineStr">
@@ -59828,18 +58620,6 @@
           <t>[(24000, 9849675, 13529475), (23000, 9390450, 11640600), (22000, 8835000, 9850875)]</t>
         </is>
       </c>
-      <c r="AB564" t="inlineStr"/>
-      <c r="AC564" t="inlineStr"/>
-      <c r="AD564" t="inlineStr"/>
-      <c r="AE564" t="inlineStr"/>
-      <c r="AF564" t="inlineStr"/>
-      <c r="AG564" t="inlineStr"/>
-      <c r="AH564" t="inlineStr"/>
-      <c r="AI564" t="inlineStr"/>
-      <c r="AJ564" t="inlineStr"/>
-      <c r="AK564" t="inlineStr"/>
-      <c r="AL564" t="inlineStr"/>
-      <c r="AM564" t="inlineStr"/>
     </row>
     <row r="565">
       <c r="A565" t="inlineStr">
@@ -59943,18 +58723,6 @@
           <t>[(24000, 9750900, 13429800), (23000, 9436800, 11686950), (22000, 8865075, 9879675)]</t>
         </is>
       </c>
-      <c r="AB565" t="inlineStr"/>
-      <c r="AC565" t="inlineStr"/>
-      <c r="AD565" t="inlineStr"/>
-      <c r="AE565" t="inlineStr"/>
-      <c r="AF565" t="inlineStr"/>
-      <c r="AG565" t="inlineStr"/>
-      <c r="AH565" t="inlineStr"/>
-      <c r="AI565" t="inlineStr"/>
-      <c r="AJ565" t="inlineStr"/>
-      <c r="AK565" t="inlineStr"/>
-      <c r="AL565" t="inlineStr"/>
-      <c r="AM565" t="inlineStr"/>
     </row>
     <row r="566">
       <c r="A566" t="inlineStr">
@@ -60058,18 +58826,6 @@
           <t>[(24000, 9750900, 13429800), (23000, 9436800, 11686950), (22000, 8865075, 9879675)]</t>
         </is>
       </c>
-      <c r="AB566" t="inlineStr"/>
-      <c r="AC566" t="inlineStr"/>
-      <c r="AD566" t="inlineStr"/>
-      <c r="AE566" t="inlineStr"/>
-      <c r="AF566" t="inlineStr"/>
-      <c r="AG566" t="inlineStr"/>
-      <c r="AH566" t="inlineStr"/>
-      <c r="AI566" t="inlineStr"/>
-      <c r="AJ566" t="inlineStr"/>
-      <c r="AK566" t="inlineStr"/>
-      <c r="AL566" t="inlineStr"/>
-      <c r="AM566" t="inlineStr"/>
     </row>
     <row r="567">
       <c r="A567" t="inlineStr">
@@ -60173,18 +58929,6 @@
           <t>[(24000, 9750900, 13429800), (23000, 9436800, 11688375), (22000, 8865075, 9879675)]</t>
         </is>
       </c>
-      <c r="AB567" t="inlineStr"/>
-      <c r="AC567" t="inlineStr"/>
-      <c r="AD567" t="inlineStr"/>
-      <c r="AE567" t="inlineStr"/>
-      <c r="AF567" t="inlineStr"/>
-      <c r="AG567" t="inlineStr"/>
-      <c r="AH567" t="inlineStr"/>
-      <c r="AI567" t="inlineStr"/>
-      <c r="AJ567" t="inlineStr"/>
-      <c r="AK567" t="inlineStr"/>
-      <c r="AL567" t="inlineStr"/>
-      <c r="AM567" t="inlineStr"/>
     </row>
     <row r="568">
       <c r="A568" t="inlineStr">
@@ -60288,18 +59032,6 @@
           <t>[(24000, 9750900, 13429800), (23000, 9436800, 11688375), (22000, 8865075, 9879675)]</t>
         </is>
       </c>
-      <c r="AB568" t="inlineStr"/>
-      <c r="AC568" t="inlineStr"/>
-      <c r="AD568" t="inlineStr"/>
-      <c r="AE568" t="inlineStr"/>
-      <c r="AF568" t="inlineStr"/>
-      <c r="AG568" t="inlineStr"/>
-      <c r="AH568" t="inlineStr"/>
-      <c r="AI568" t="inlineStr"/>
-      <c r="AJ568" t="inlineStr"/>
-      <c r="AK568" t="inlineStr"/>
-      <c r="AL568" t="inlineStr"/>
-      <c r="AM568" t="inlineStr"/>
     </row>
     <row r="569">
       <c r="A569" t="inlineStr">
@@ -60403,18 +59135,6 @@
           <t>[(24000, 9682275, 13356450), (23000, 9304575, 11556300), (22000, 8882550, 9897150)]</t>
         </is>
       </c>
-      <c r="AB569" t="inlineStr"/>
-      <c r="AC569" t="inlineStr"/>
-      <c r="AD569" t="inlineStr"/>
-      <c r="AE569" t="inlineStr"/>
-      <c r="AF569" t="inlineStr"/>
-      <c r="AG569" t="inlineStr"/>
-      <c r="AH569" t="inlineStr"/>
-      <c r="AI569" t="inlineStr"/>
-      <c r="AJ569" t="inlineStr"/>
-      <c r="AK569" t="inlineStr"/>
-      <c r="AL569" t="inlineStr"/>
-      <c r="AM569" t="inlineStr"/>
     </row>
     <row r="570">
       <c r="A570" t="inlineStr">
@@ -60518,18 +59238,6 @@
           <t>[(24000, 9682275, 13356450), (23000, 9304575, 11556300), (22000, 8882550, 9897150)]</t>
         </is>
       </c>
-      <c r="AB570" t="inlineStr"/>
-      <c r="AC570" t="inlineStr"/>
-      <c r="AD570" t="inlineStr"/>
-      <c r="AE570" t="inlineStr"/>
-      <c r="AF570" t="inlineStr"/>
-      <c r="AG570" t="inlineStr"/>
-      <c r="AH570" t="inlineStr"/>
-      <c r="AI570" t="inlineStr"/>
-      <c r="AJ570" t="inlineStr"/>
-      <c r="AK570" t="inlineStr"/>
-      <c r="AL570" t="inlineStr"/>
-      <c r="AM570" t="inlineStr"/>
     </row>
     <row r="571">
       <c r="A571" t="inlineStr">
@@ -60633,18 +59341,6 @@
           <t>[(24000, 9316725, 12985350), (23000, 9106650, 11358525), (22000, 8650125, 9664725)]</t>
         </is>
       </c>
-      <c r="AB571" t="inlineStr"/>
-      <c r="AC571" t="inlineStr"/>
-      <c r="AD571" t="inlineStr"/>
-      <c r="AE571" t="inlineStr"/>
-      <c r="AF571" t="inlineStr"/>
-      <c r="AG571" t="inlineStr"/>
-      <c r="AH571" t="inlineStr"/>
-      <c r="AI571" t="inlineStr"/>
-      <c r="AJ571" t="inlineStr"/>
-      <c r="AK571" t="inlineStr"/>
-      <c r="AL571" t="inlineStr"/>
-      <c r="AM571" t="inlineStr"/>
     </row>
     <row r="572">
       <c r="A572" t="inlineStr">
@@ -60748,18 +59444,6 @@
           <t>[(24000, 9316725, 12985350), (23000, 9106650, 11358525), (22000, 8650125, 9664725)]</t>
         </is>
       </c>
-      <c r="AB572" t="inlineStr"/>
-      <c r="AC572" t="inlineStr"/>
-      <c r="AD572" t="inlineStr"/>
-      <c r="AE572" t="inlineStr"/>
-      <c r="AF572" t="inlineStr"/>
-      <c r="AG572" t="inlineStr"/>
-      <c r="AH572" t="inlineStr"/>
-      <c r="AI572" t="inlineStr"/>
-      <c r="AJ572" t="inlineStr"/>
-      <c r="AK572" t="inlineStr"/>
-      <c r="AL572" t="inlineStr"/>
-      <c r="AM572" t="inlineStr"/>
     </row>
     <row r="573">
       <c r="A573" t="inlineStr">
@@ -60863,18 +59547,6 @@
           <t>[(24000, 9316725, 12985350), (23000, 9106650, 11358525), (22000, 8650125, 9664725)]</t>
         </is>
       </c>
-      <c r="AB573" t="inlineStr"/>
-      <c r="AC573" t="inlineStr"/>
-      <c r="AD573" t="inlineStr"/>
-      <c r="AE573" t="inlineStr"/>
-      <c r="AF573" t="inlineStr"/>
-      <c r="AG573" t="inlineStr"/>
-      <c r="AH573" t="inlineStr"/>
-      <c r="AI573" t="inlineStr"/>
-      <c r="AJ573" t="inlineStr"/>
-      <c r="AK573" t="inlineStr"/>
-      <c r="AL573" t="inlineStr"/>
-      <c r="AM573" t="inlineStr"/>
     </row>
     <row r="574">
       <c r="A574" t="inlineStr">
@@ -60978,18 +59650,6 @@
           <t>[(24000, 9316725, 12985350), (23000, 9106650, 11358525), (22000, 8650125, 9664725)]</t>
         </is>
       </c>
-      <c r="AB574" t="inlineStr"/>
-      <c r="AC574" t="inlineStr"/>
-      <c r="AD574" t="inlineStr"/>
-      <c r="AE574" t="inlineStr"/>
-      <c r="AF574" t="inlineStr"/>
-      <c r="AG574" t="inlineStr"/>
-      <c r="AH574" t="inlineStr"/>
-      <c r="AI574" t="inlineStr"/>
-      <c r="AJ574" t="inlineStr"/>
-      <c r="AK574" t="inlineStr"/>
-      <c r="AL574" t="inlineStr"/>
-      <c r="AM574" t="inlineStr"/>
     </row>
     <row r="575">
       <c r="A575" t="inlineStr">
@@ -61093,18 +59753,6 @@
           <t>[(24000, 9316725, 12985350), (23000, 9106650, 11358525), (22000, 8650125, 9664725)]</t>
         </is>
       </c>
-      <c r="AB575" t="inlineStr"/>
-      <c r="AC575" t="inlineStr"/>
-      <c r="AD575" t="inlineStr"/>
-      <c r="AE575" t="inlineStr"/>
-      <c r="AF575" t="inlineStr"/>
-      <c r="AG575" t="inlineStr"/>
-      <c r="AH575" t="inlineStr"/>
-      <c r="AI575" t="inlineStr"/>
-      <c r="AJ575" t="inlineStr"/>
-      <c r="AK575" t="inlineStr"/>
-      <c r="AL575" t="inlineStr"/>
-      <c r="AM575" t="inlineStr"/>
     </row>
     <row r="576">
       <c r="A576" t="inlineStr">
@@ -61208,18 +59856,6 @@
           <t>[(24000, 9316725, 12985350), (23000, 9106650, 11358525), (22000, 8650125, 9664725)]</t>
         </is>
       </c>
-      <c r="AB576" t="inlineStr"/>
-      <c r="AC576" t="inlineStr"/>
-      <c r="AD576" t="inlineStr"/>
-      <c r="AE576" t="inlineStr"/>
-      <c r="AF576" t="inlineStr"/>
-      <c r="AG576" t="inlineStr"/>
-      <c r="AH576" t="inlineStr"/>
-      <c r="AI576" t="inlineStr"/>
-      <c r="AJ576" t="inlineStr"/>
-      <c r="AK576" t="inlineStr"/>
-      <c r="AL576" t="inlineStr"/>
-      <c r="AM576" t="inlineStr"/>
     </row>
     <row r="577">
       <c r="A577" t="inlineStr">
@@ -61323,18 +59959,6 @@
           <t>[(24000, 9316725, 12985350), (23000, 9106650, 11358525), (22000, 8650125, 9664725)]</t>
         </is>
       </c>
-      <c r="AB577" t="inlineStr"/>
-      <c r="AC577" t="inlineStr"/>
-      <c r="AD577" t="inlineStr"/>
-      <c r="AE577" t="inlineStr"/>
-      <c r="AF577" t="inlineStr"/>
-      <c r="AG577" t="inlineStr"/>
-      <c r="AH577" t="inlineStr"/>
-      <c r="AI577" t="inlineStr"/>
-      <c r="AJ577" t="inlineStr"/>
-      <c r="AK577" t="inlineStr"/>
-      <c r="AL577" t="inlineStr"/>
-      <c r="AM577" t="inlineStr"/>
     </row>
     <row r="578">
       <c r="A578" t="inlineStr">
@@ -61438,18 +60062,6 @@
           <t>[(24000, 9316725, 12985350), (23000, 9106650, 11358525), (22000, 8650125, 9664725)]</t>
         </is>
       </c>
-      <c r="AB578" t="inlineStr"/>
-      <c r="AC578" t="inlineStr"/>
-      <c r="AD578" t="inlineStr"/>
-      <c r="AE578" t="inlineStr"/>
-      <c r="AF578" t="inlineStr"/>
-      <c r="AG578" t="inlineStr"/>
-      <c r="AH578" t="inlineStr"/>
-      <c r="AI578" t="inlineStr"/>
-      <c r="AJ578" t="inlineStr"/>
-      <c r="AK578" t="inlineStr"/>
-      <c r="AL578" t="inlineStr"/>
-      <c r="AM578" t="inlineStr"/>
     </row>
     <row r="579">
       <c r="A579" t="inlineStr">
@@ -61553,18 +60165,6 @@
           <t>[(24000, 9316725, 12985350), (23000, 9106650, 11358525), (22000, 8650125, 9664725)]</t>
         </is>
       </c>
-      <c r="AB579" t="inlineStr"/>
-      <c r="AC579" t="inlineStr"/>
-      <c r="AD579" t="inlineStr"/>
-      <c r="AE579" t="inlineStr"/>
-      <c r="AF579" t="inlineStr"/>
-      <c r="AG579" t="inlineStr"/>
-      <c r="AH579" t="inlineStr"/>
-      <c r="AI579" t="inlineStr"/>
-      <c r="AJ579" t="inlineStr"/>
-      <c r="AK579" t="inlineStr"/>
-      <c r="AL579" t="inlineStr"/>
-      <c r="AM579" t="inlineStr"/>
     </row>
     <row r="580">
       <c r="A580" t="inlineStr">
@@ -61668,18 +60268,6 @@
           <t>[(24000, 9316725, 12985350), (23000, 9106650, 11358525), (22000, 8650125, 9664725)]</t>
         </is>
       </c>
-      <c r="AB580" t="inlineStr"/>
-      <c r="AC580" t="inlineStr"/>
-      <c r="AD580" t="inlineStr"/>
-      <c r="AE580" t="inlineStr"/>
-      <c r="AF580" t="inlineStr"/>
-      <c r="AG580" t="inlineStr"/>
-      <c r="AH580" t="inlineStr"/>
-      <c r="AI580" t="inlineStr"/>
-      <c r="AJ580" t="inlineStr"/>
-      <c r="AK580" t="inlineStr"/>
-      <c r="AL580" t="inlineStr"/>
-      <c r="AM580" t="inlineStr"/>
     </row>
     <row r="581">
       <c r="A581" t="inlineStr">
@@ -61783,18 +60371,6 @@
           <t>[(24000, 9316725, 12985350), (23000, 9106650, 11358525), (22000, 8650125, 9664725)]</t>
         </is>
       </c>
-      <c r="AB581" t="inlineStr"/>
-      <c r="AC581" t="inlineStr"/>
-      <c r="AD581" t="inlineStr"/>
-      <c r="AE581" t="inlineStr"/>
-      <c r="AF581" t="inlineStr"/>
-      <c r="AG581" t="inlineStr"/>
-      <c r="AH581" t="inlineStr"/>
-      <c r="AI581" t="inlineStr"/>
-      <c r="AJ581" t="inlineStr"/>
-      <c r="AK581" t="inlineStr"/>
-      <c r="AL581" t="inlineStr"/>
-      <c r="AM581" t="inlineStr"/>
     </row>
     <row r="582">
       <c r="A582" t="inlineStr">
@@ -61898,18 +60474,236 @@
           <t>[(24000, 9316725, 12985350), (23000, 9106650, 11358525), (22000, 8650125, 9664725)]</t>
         </is>
       </c>
-      <c r="AB582" t="inlineStr"/>
-      <c r="AC582" t="inlineStr"/>
-      <c r="AD582" t="inlineStr"/>
-      <c r="AE582" t="inlineStr"/>
-      <c r="AF582" t="inlineStr"/>
-      <c r="AG582" t="inlineStr"/>
-      <c r="AH582" t="inlineStr"/>
-      <c r="AI582" t="inlineStr"/>
-      <c r="AJ582" t="inlineStr"/>
-      <c r="AK582" t="inlineStr"/>
-      <c r="AL582" t="inlineStr"/>
-      <c r="AM582" t="inlineStr"/>
+    </row>
+    <row r="583">
+      <c r="A583" t="inlineStr">
+        <is>
+          <t>14:37:35</t>
+        </is>
+      </c>
+      <c r="B583" t="n">
+        <v>24176.15</v>
+      </c>
+      <c r="C583" t="n">
+        <v>24200</v>
+      </c>
+      <c r="D583" t="n">
+        <v>179384850</v>
+      </c>
+      <c r="E583" t="n">
+        <v>142642950</v>
+      </c>
+      <c r="F583" t="n">
+        <v>35369850</v>
+      </c>
+      <c r="G583" t="n">
+        <v>-2531400</v>
+      </c>
+      <c r="H583" t="n">
+        <v>26586600</v>
+      </c>
+      <c r="I583" t="n">
+        <v>23812725</v>
+      </c>
+      <c r="J583" t="n">
+        <v>11178750</v>
+      </c>
+      <c r="K583" t="n">
+        <v>-583425</v>
+      </c>
+      <c r="L583" t="n">
+        <v>0.7951783553627857</v>
+      </c>
+      <c r="M583" t="n">
+        <v>0.8956664259438966</v>
+      </c>
+      <c r="N583" t="n">
+        <v>0.05219054008721905</v>
+      </c>
+      <c r="O583" t="n">
+        <v>93.32106460868705</v>
+      </c>
+      <c r="P583" t="n">
+        <v>6.678935391312951</v>
+      </c>
+      <c r="Q583" t="n">
+        <v>95.03982044137246</v>
+      </c>
+      <c r="R583" t="n">
+        <v>4.96017955862755</v>
+      </c>
+      <c r="S583" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T583" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U583" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V583" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W583" t="inlineStr">
+        <is>
+          <t>[25500, 24500, 25000]</t>
+        </is>
+      </c>
+      <c r="X583" t="inlineStr">
+        <is>
+          <t>[23500, 23000, 24000]</t>
+        </is>
+      </c>
+      <c r="Y583" t="inlineStr">
+        <is>
+          <t>BEARISH</t>
+        </is>
+      </c>
+      <c r="Z583" t="inlineStr">
+        <is>
+          <t>[(25500, 13411650, 13663575), (24500, 11401950, 12867675), (25000, 10369200, 10993575)]</t>
+        </is>
+      </c>
+      <c r="AA583" t="inlineStr">
+        <is>
+          <t>[(23500, 9453000, 9915600), (23000, 8447250, 8584650), (24000, 8358750, 10815525)]</t>
+        </is>
+      </c>
+      <c r="AB583" t="inlineStr"/>
+      <c r="AC583" t="inlineStr"/>
+      <c r="AD583" t="inlineStr"/>
+      <c r="AE583" t="inlineStr"/>
+      <c r="AF583" t="inlineStr"/>
+      <c r="AG583" t="inlineStr"/>
+      <c r="AH583" t="inlineStr"/>
+      <c r="AI583" t="inlineStr"/>
+      <c r="AJ583" t="inlineStr"/>
+      <c r="AK583" t="inlineStr"/>
+      <c r="AL583" t="inlineStr"/>
+      <c r="AM583" t="inlineStr"/>
+    </row>
+    <row r="584">
+      <c r="A584" t="inlineStr">
+        <is>
+          <t>14:38:37</t>
+        </is>
+      </c>
+      <c r="B584" t="n">
+        <v>24176.15</v>
+      </c>
+      <c r="C584" t="n">
+        <v>24200</v>
+      </c>
+      <c r="D584" t="n">
+        <v>179384850</v>
+      </c>
+      <c r="E584" t="n">
+        <v>142642950</v>
+      </c>
+      <c r="F584" t="n">
+        <v>35369850</v>
+      </c>
+      <c r="G584" t="n">
+        <v>-2531400</v>
+      </c>
+      <c r="H584" t="n">
+        <v>26586600</v>
+      </c>
+      <c r="I584" t="n">
+        <v>23812725</v>
+      </c>
+      <c r="J584" t="n">
+        <v>11178750</v>
+      </c>
+      <c r="K584" t="n">
+        <v>-583425</v>
+      </c>
+      <c r="L584" t="n">
+        <v>0.7951783553627857</v>
+      </c>
+      <c r="M584" t="n">
+        <v>0.8956664259438966</v>
+      </c>
+      <c r="N584" t="n">
+        <v>0.05219054008721905</v>
+      </c>
+      <c r="O584" t="n">
+        <v>93.32106460868705</v>
+      </c>
+      <c r="P584" t="n">
+        <v>6.678935391312951</v>
+      </c>
+      <c r="Q584" t="n">
+        <v>95.03982044137246</v>
+      </c>
+      <c r="R584" t="n">
+        <v>4.96017955862755</v>
+      </c>
+      <c r="S584" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="T584" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="U584" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="V584" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="W584" t="inlineStr">
+        <is>
+          <t>[25500, 24500, 25000]</t>
+        </is>
+      </c>
+      <c r="X584" t="inlineStr">
+        <is>
+          <t>[23500, 23000, 24000]</t>
+        </is>
+      </c>
+      <c r="Y584" t="inlineStr">
+        <is>
+          <t>BEARISH</t>
+        </is>
+      </c>
+      <c r="Z584" t="inlineStr">
+        <is>
+          <t>[(25500, 13411650, 13663575), (24500, 11401950, 12867675), (25000, 10369200, 10993575)]</t>
+        </is>
+      </c>
+      <c r="AA584" t="inlineStr">
+        <is>
+          <t>[(23500, 9453000, 9915600), (23000, 8447250, 8584650), (24000, 8358750, 10815525)]</t>
+        </is>
+      </c>
+      <c r="AB584" t="inlineStr"/>
+      <c r="AC584" t="inlineStr"/>
+      <c r="AD584" t="inlineStr"/>
+      <c r="AE584" t="inlineStr"/>
+      <c r="AF584" t="inlineStr"/>
+      <c r="AG584" t="inlineStr"/>
+      <c r="AH584" t="inlineStr"/>
+      <c r="AI584" t="inlineStr"/>
+      <c r="AJ584" t="inlineStr"/>
+      <c r="AK584" t="inlineStr"/>
+      <c r="AL584" t="inlineStr"/>
+      <c r="AM584" t="inlineStr"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="D2:D9435">
